--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1964A820-CA2A-493E-B1F8-732076F8C5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F49453C-6939-45D7-9100-50B952CAF692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AF_Trans" sheetId="20" r:id="rId1"/>
@@ -200,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="75">
   <si>
     <t>~TFM_INS</t>
   </si>
@@ -422,6 +422,9 @@
   </si>
   <si>
     <t>SOLPV</t>
+  </si>
+  <si>
+    <t>CSP</t>
   </si>
 </sst>
 </file>
@@ -579,7 +582,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -602,7 +605,6 @@
     <xf numFmtId="165" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFill="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -919,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E39CA8-E622-4EC6-B5A7-6B0C4E956FF0}">
-  <dimension ref="B3:O102"/>
+  <dimension ref="B3:O150"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -1833,7 +1835,7 @@
       <c r="G55" s="16">
         <v>0</v>
       </c>
-      <c r="I55" s="18" t="s">
+      <c r="I55" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1850,7 +1852,7 @@
       <c r="G56" s="16">
         <v>0</v>
       </c>
-      <c r="I56" s="18" t="s">
+      <c r="I56" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1867,7 +1869,7 @@
       <c r="G57" s="17">
         <v>0</v>
       </c>
-      <c r="I57" s="18" t="s">
+      <c r="I57" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1884,7 +1886,7 @@
       <c r="G58" s="17">
         <v>0</v>
       </c>
-      <c r="I58" s="18" t="s">
+      <c r="I58" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1901,7 +1903,7 @@
       <c r="G59" s="17">
         <v>0</v>
       </c>
-      <c r="I59" s="18" t="s">
+      <c r="I59" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1918,7 +1920,7 @@
       <c r="G60" s="17">
         <v>0</v>
       </c>
-      <c r="I60" s="18" t="s">
+      <c r="I60" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1935,7 +1937,7 @@
       <c r="G61" s="17">
         <v>6.9165519713261618E-3</v>
       </c>
-      <c r="I61" s="18" t="s">
+      <c r="I61" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1952,7 +1954,7 @@
       <c r="G62" s="17">
         <v>4.9742853046594968E-2</v>
       </c>
-      <c r="I62" s="18" t="s">
+      <c r="I62" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1969,7 +1971,7 @@
       <c r="G63" s="17">
         <v>0.12554577777777776</v>
       </c>
-      <c r="I63" s="18" t="s">
+      <c r="I63" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1986,7 +1988,7 @@
       <c r="G64" s="17">
         <v>0.2058007025089606</v>
       </c>
-      <c r="I64" s="18" t="s">
+      <c r="I64" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2003,7 +2005,7 @@
       <c r="G65" s="17">
         <v>0.27468446594982077</v>
       </c>
-      <c r="I65" s="18" t="s">
+      <c r="I65" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2020,7 +2022,7 @@
       <c r="G66" s="17">
         <v>0.32637437275985665</v>
       </c>
-      <c r="I66" s="18" t="s">
+      <c r="I66" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2037,7 +2039,7 @@
       <c r="G67" s="17">
         <v>0.35267560573476697</v>
       </c>
-      <c r="I67" s="18" t="s">
+      <c r="I67" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2054,7 +2056,7 @@
       <c r="G68" s="17">
         <v>0.34322033691756271</v>
       </c>
-      <c r="I68" s="18" t="s">
+      <c r="I68" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2071,7 +2073,7 @@
       <c r="G69" s="17">
         <v>0.30308891039426522</v>
       </c>
-      <c r="I69" s="18" t="s">
+      <c r="I69" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2088,7 +2090,7 @@
       <c r="G70" s="17">
         <v>0.23170381362007167</v>
       </c>
-      <c r="I70" s="18" t="s">
+      <c r="I70" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2105,7 +2107,7 @@
       <c r="G71" s="17">
         <v>0.14172651612903225</v>
       </c>
-      <c r="I71" s="18" t="s">
+      <c r="I71" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2122,7 +2124,7 @@
       <c r="G72" s="16">
         <v>5.3895483870967743E-2</v>
       </c>
-      <c r="I72" s="18" t="s">
+      <c r="I72" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2139,7 +2141,7 @@
       <c r="G73" s="16">
         <v>2.6301935483870969E-3</v>
       </c>
-      <c r="I73" s="18" t="s">
+      <c r="I73" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2156,7 +2158,7 @@
       <c r="G74" s="16">
         <v>0</v>
       </c>
-      <c r="I74" s="18" t="s">
+      <c r="I74" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2173,7 +2175,7 @@
       <c r="G75" s="16">
         <v>0</v>
       </c>
-      <c r="I75" s="18" t="s">
+      <c r="I75" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2190,7 +2192,7 @@
       <c r="G76" s="16">
         <v>0</v>
       </c>
-      <c r="I76" s="18" t="s">
+      <c r="I76" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2207,7 +2209,7 @@
       <c r="G77" s="16">
         <v>0</v>
       </c>
-      <c r="I77" s="18" t="s">
+      <c r="I77" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2224,7 +2226,7 @@
       <c r="G78" s="16">
         <v>0</v>
       </c>
-      <c r="I78" s="18" t="s">
+      <c r="I78" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2241,7 +2243,7 @@
       <c r="G79" s="16">
         <v>0</v>
       </c>
-      <c r="I79" s="18" t="s">
+      <c r="I79" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2258,7 +2260,7 @@
       <c r="G80" s="16">
         <v>0</v>
       </c>
-      <c r="I80" s="18" t="s">
+      <c r="I80" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2275,7 +2277,7 @@
       <c r="G81" s="16">
         <v>0</v>
       </c>
-      <c r="I81" s="18" t="s">
+      <c r="I81" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2292,7 +2294,7 @@
       <c r="G82" s="16">
         <v>0</v>
       </c>
-      <c r="I82" s="18" t="s">
+      <c r="I82" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2309,7 +2311,7 @@
       <c r="G83" s="16">
         <v>0</v>
       </c>
-      <c r="I83" s="18" t="s">
+      <c r="I83" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2326,7 +2328,7 @@
       <c r="G84" s="16">
         <v>0</v>
       </c>
-      <c r="I84" s="18" t="s">
+      <c r="I84" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2343,7 +2345,7 @@
       <c r="G85" s="16">
         <v>6.4190919952210254E-3</v>
       </c>
-      <c r="I85" s="18" t="s">
+      <c r="I85" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2360,7 +2362,7 @@
       <c r="G86" s="16">
         <v>7.0838474313022717E-2</v>
       </c>
-      <c r="I86" s="18" t="s">
+      <c r="I86" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2377,7 +2379,7 @@
       <c r="G87" s="16">
         <v>0.15999428793309439</v>
       </c>
-      <c r="I87" s="18" t="s">
+      <c r="I87" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2394,7 +2396,7 @@
       <c r="G88" s="16">
         <v>0.25343209199522099</v>
       </c>
-      <c r="I88" s="18" t="s">
+      <c r="I88" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2411,7 +2413,7 @@
       <c r="G89" s="16">
         <v>0.32960197968936678</v>
       </c>
-      <c r="I89" s="18" t="s">
+      <c r="I89" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2428,7 +2430,7 @@
       <c r="G90" s="16">
         <v>0.37592762246117079</v>
       </c>
-      <c r="I90" s="18" t="s">
+      <c r="I90" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2445,7 +2447,7 @@
       <c r="G91" s="16">
         <v>0.38776096057347664</v>
       </c>
-      <c r="I91" s="18" t="s">
+      <c r="I91" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2462,7 +2464,7 @@
       <c r="G92" s="16">
         <v>0.36426783751493425</v>
       </c>
-      <c r="I92" s="18" t="s">
+      <c r="I92" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2479,7 +2481,7 @@
       <c r="G93" s="16">
         <v>0.31009156033452806</v>
       </c>
-      <c r="I93" s="18" t="s">
+      <c r="I93" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2496,7 +2498,7 @@
       <c r="G94" s="16">
         <v>0.23188419952210276</v>
       </c>
-      <c r="I94" s="18" t="s">
+      <c r="I94" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2513,7 +2515,7 @@
       <c r="G95" s="16">
         <v>0.13618056033452808</v>
       </c>
-      <c r="I95" s="18" t="s">
+      <c r="I95" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2530,7 +2532,7 @@
       <c r="G96" s="16">
         <v>4.9357593787335743E-2</v>
       </c>
-      <c r="I96" s="18" t="s">
+      <c r="I96" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2547,7 +2549,7 @@
       <c r="G97" s="16">
         <v>7.5268817204301086E-6</v>
       </c>
-      <c r="I97" s="18" t="s">
+      <c r="I97" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2564,7 +2566,7 @@
       <c r="G98" s="16">
         <v>0</v>
       </c>
-      <c r="I98" s="18" t="s">
+      <c r="I98" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2581,7 +2583,7 @@
       <c r="G99" s="16">
         <v>0</v>
       </c>
-      <c r="I99" s="18" t="s">
+      <c r="I99" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2598,7 +2600,7 @@
       <c r="G100" s="16">
         <v>0</v>
       </c>
-      <c r="I100" s="18" t="s">
+      <c r="I100" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2615,7 +2617,7 @@
       <c r="G101" s="16">
         <v>0</v>
       </c>
-      <c r="I101" s="18" t="s">
+      <c r="I101" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2632,8 +2634,824 @@
       <c r="G102" s="17">
         <v>0</v>
       </c>
-      <c r="I102" s="18" t="s">
-        <v>73</v>
+      <c r="I102" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B103" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103">
+        <v>2030</v>
+      </c>
+      <c r="G103" s="16">
+        <v>1</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B104" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104">
+        <v>2030</v>
+      </c>
+      <c r="G104" s="16">
+        <v>1</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B105" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105">
+        <v>2030</v>
+      </c>
+      <c r="G105" s="16">
+        <v>1</v>
+      </c>
+      <c r="I105" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B106" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106">
+        <v>2030</v>
+      </c>
+      <c r="G106" s="16">
+        <v>1</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B107" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D107" t="s">
+        <v>23</v>
+      </c>
+      <c r="E107">
+        <v>2030</v>
+      </c>
+      <c r="G107" s="16">
+        <v>1</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B108" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108">
+        <v>2030</v>
+      </c>
+      <c r="G108" s="16">
+        <v>1</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B109" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109">
+        <v>2030</v>
+      </c>
+      <c r="G109" s="16">
+        <v>1</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110">
+        <v>2030</v>
+      </c>
+      <c r="G110" s="16">
+        <v>1</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111">
+        <v>2030</v>
+      </c>
+      <c r="G111" s="16">
+        <v>1</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112">
+        <v>2030</v>
+      </c>
+      <c r="G112" s="16">
+        <v>1</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B113" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113">
+        <v>2030</v>
+      </c>
+      <c r="G113" s="16">
+        <v>1</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B114" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D114" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114">
+        <v>2030</v>
+      </c>
+      <c r="G114" s="16">
+        <v>1</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115">
+        <v>2030</v>
+      </c>
+      <c r="G115" s="16">
+        <v>1</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116">
+        <v>2030</v>
+      </c>
+      <c r="G116" s="16">
+        <v>1</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B117" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117">
+        <v>2030</v>
+      </c>
+      <c r="G117" s="16">
+        <v>1</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B118" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D118" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118">
+        <v>2030</v>
+      </c>
+      <c r="G118" s="16">
+        <v>1</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B119" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119">
+        <v>2030</v>
+      </c>
+      <c r="G119" s="16">
+        <v>1</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120">
+        <v>2030</v>
+      </c>
+      <c r="G120" s="16">
+        <v>1</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D121" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121">
+        <v>2030</v>
+      </c>
+      <c r="G121" s="16">
+        <v>1</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B122" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D122" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122">
+        <v>2030</v>
+      </c>
+      <c r="G122" s="16">
+        <v>1</v>
+      </c>
+      <c r="I122" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B123" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D123" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123">
+        <v>2030</v>
+      </c>
+      <c r="G123" s="16">
+        <v>1</v>
+      </c>
+      <c r="I123" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B124" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D124" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124">
+        <v>2030</v>
+      </c>
+      <c r="G124" s="16">
+        <v>1</v>
+      </c>
+      <c r="I124" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B125" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125">
+        <v>2030</v>
+      </c>
+      <c r="G125" s="16">
+        <v>1</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B126" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D126" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126">
+        <v>2030</v>
+      </c>
+      <c r="G126" s="16">
+        <v>1</v>
+      </c>
+      <c r="I126" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B127" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D127" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127">
+        <v>2030</v>
+      </c>
+      <c r="G127" s="16">
+        <v>1</v>
+      </c>
+      <c r="I127" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B128" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128">
+        <v>2030</v>
+      </c>
+      <c r="G128" s="16">
+        <v>1</v>
+      </c>
+      <c r="I128" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B129" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129">
+        <v>2030</v>
+      </c>
+      <c r="G129" s="16">
+        <v>1</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B130" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130">
+        <v>2030</v>
+      </c>
+      <c r="G130" s="16">
+        <v>1</v>
+      </c>
+      <c r="I130" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B131" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D131" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131">
+        <v>2030</v>
+      </c>
+      <c r="G131" s="16">
+        <v>1</v>
+      </c>
+      <c r="I131" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B132" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D132" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132">
+        <v>2030</v>
+      </c>
+      <c r="G132" s="16">
+        <v>1</v>
+      </c>
+      <c r="I132" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B133" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D133" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133">
+        <v>2030</v>
+      </c>
+      <c r="G133" s="16">
+        <v>1</v>
+      </c>
+      <c r="I133" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B134" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D134" t="s">
+        <v>23</v>
+      </c>
+      <c r="E134">
+        <v>2030</v>
+      </c>
+      <c r="G134" s="16">
+        <v>1</v>
+      </c>
+      <c r="I134" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B135" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D135" t="s">
+        <v>23</v>
+      </c>
+      <c r="E135">
+        <v>2030</v>
+      </c>
+      <c r="G135" s="16">
+        <v>1</v>
+      </c>
+      <c r="I135" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B136" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D136" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136">
+        <v>2030</v>
+      </c>
+      <c r="G136" s="16">
+        <v>1</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B137" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137">
+        <v>2030</v>
+      </c>
+      <c r="G137" s="16">
+        <v>1</v>
+      </c>
+      <c r="I137" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B138" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D138" t="s">
+        <v>23</v>
+      </c>
+      <c r="E138">
+        <v>2030</v>
+      </c>
+      <c r="G138" s="16">
+        <v>1</v>
+      </c>
+      <c r="I138" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B139" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139" t="s">
+        <v>23</v>
+      </c>
+      <c r="E139">
+        <v>2030</v>
+      </c>
+      <c r="G139" s="16">
+        <v>1</v>
+      </c>
+      <c r="I139" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B140" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D140" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140">
+        <v>2030</v>
+      </c>
+      <c r="G140" s="16">
+        <v>1</v>
+      </c>
+      <c r="I140" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B141" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D141" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141">
+        <v>2030</v>
+      </c>
+      <c r="G141" s="16">
+        <v>1</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B142" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D142" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142">
+        <v>2030</v>
+      </c>
+      <c r="G142" s="16">
+        <v>1</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B143" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D143" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143">
+        <v>2030</v>
+      </c>
+      <c r="G143" s="16">
+        <v>1</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B144" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D144" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144">
+        <v>2030</v>
+      </c>
+      <c r="G144" s="16">
+        <v>1</v>
+      </c>
+      <c r="I144" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B145" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D145" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145">
+        <v>2030</v>
+      </c>
+      <c r="G145" s="16">
+        <v>1</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B146" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D146" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146">
+        <v>2030</v>
+      </c>
+      <c r="G146" s="16">
+        <v>1</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B147" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147">
+        <v>2030</v>
+      </c>
+      <c r="G147" s="16">
+        <v>1</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B148" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D148" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148">
+        <v>2030</v>
+      </c>
+      <c r="G148" s="16">
+        <v>1</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B149" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D149" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149">
+        <v>2030</v>
+      </c>
+      <c r="G149" s="16">
+        <v>1</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B150" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D150" t="s">
+        <v>23</v>
+      </c>
+      <c r="E150">
+        <v>2030</v>
+      </c>
+      <c r="G150" s="16">
+        <v>1</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -1,27 +1,79 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\INDIND\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77582279-FBE0-4DDC-84B9-EC47BBE4AC03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F49453C-6939-45D7-9100-50B952CAF692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="AVA" sheetId="18" r:id="rId1"/>
-    <sheet name="Trans Tables" sheetId="17" r:id="rId2"/>
-    <sheet name="FILL Table" sheetId="19" r:id="rId3"/>
+    <sheet name="AF_Trans" sheetId="20" r:id="rId1"/>
+    <sheet name="AVA" sheetId="18" r:id="rId2"/>
+    <sheet name="Trans Tables" sheetId="17" r:id="rId3"/>
+    <sheet name="FILL Table" sheetId="19" r:id="rId4"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Maurizio Gargiulo</author>
+    <author>Gary Goldstein</author>
+  </authors>
+  <commentList>
+    <comment ref="B5" authorId="0" shapeId="0" xr:uid="{FF4C519A-314E-423E-AB0E-6C67D9487774}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Insert Table</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H5" authorId="1" shapeId="0" xr:uid="{E8EB0170-ECE9-4105-9C5E-D0FA4C98A1FF}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Define the qualifiers based upon technology set + topology + name + descriptions, according to both include and exclude specifications.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M5" authorId="1" shapeId="0" xr:uid="{CAECD70C-56F0-4299-8C63-07891A7137F0}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Define the qualifiers based upon commodity set + name + descriptions, according to both include and exclude specifications.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Amit Kanudia</author>
@@ -56,7 +108,7 @@
 </comments>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Maurizio Gargiulo</author>
@@ -148,7 +200,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="75">
   <si>
     <t>~TFM_INS</t>
   </si>
@@ -217,16 +269,173 @@
   </si>
   <si>
     <t>ETH</t>
+  </si>
+  <si>
+    <t>AF</t>
+  </si>
+  <si>
+    <t>W_01</t>
+  </si>
+  <si>
+    <t>W_02</t>
+  </si>
+  <si>
+    <t>W_03</t>
+  </si>
+  <si>
+    <t>W_04</t>
+  </si>
+  <si>
+    <t>W_05</t>
+  </si>
+  <si>
+    <t>W_06</t>
+  </si>
+  <si>
+    <t>W_07</t>
+  </si>
+  <si>
+    <t>W_08</t>
+  </si>
+  <si>
+    <t>W_09</t>
+  </si>
+  <si>
+    <t>W_10</t>
+  </si>
+  <si>
+    <t>W_11</t>
+  </si>
+  <si>
+    <t>W_12</t>
+  </si>
+  <si>
+    <t>W_13</t>
+  </si>
+  <si>
+    <t>W_14</t>
+  </si>
+  <si>
+    <t>W_15</t>
+  </si>
+  <si>
+    <t>W_16</t>
+  </si>
+  <si>
+    <t>W_17</t>
+  </si>
+  <si>
+    <t>W_18</t>
+  </si>
+  <si>
+    <t>W_19</t>
+  </si>
+  <si>
+    <t>W_20</t>
+  </si>
+  <si>
+    <t>W_21</t>
+  </si>
+  <si>
+    <t>W_22</t>
+  </si>
+  <si>
+    <t>W_23</t>
+  </si>
+  <si>
+    <t>W_24</t>
+  </si>
+  <si>
+    <t>D_01</t>
+  </si>
+  <si>
+    <t>D_02</t>
+  </si>
+  <si>
+    <t>D_03</t>
+  </si>
+  <si>
+    <t>D_04</t>
+  </si>
+  <si>
+    <t>D_05</t>
+  </si>
+  <si>
+    <t>D_06</t>
+  </si>
+  <si>
+    <t>D_07</t>
+  </si>
+  <si>
+    <t>D_08</t>
+  </si>
+  <si>
+    <t>D_09</t>
+  </si>
+  <si>
+    <t>D_10</t>
+  </si>
+  <si>
+    <t>D_11</t>
+  </si>
+  <si>
+    <t>D_12</t>
+  </si>
+  <si>
+    <t>D_13</t>
+  </si>
+  <si>
+    <t>D_14</t>
+  </si>
+  <si>
+    <t>D_15</t>
+  </si>
+  <si>
+    <t>D_16</t>
+  </si>
+  <si>
+    <t>D_17</t>
+  </si>
+  <si>
+    <t>D_18</t>
+  </si>
+  <si>
+    <t>D_19</t>
+  </si>
+  <si>
+    <t>D_20</t>
+  </si>
+  <si>
+    <t>D_21</t>
+  </si>
+  <si>
+    <t>D_22</t>
+  </si>
+  <si>
+    <t>D_23</t>
+  </si>
+  <si>
+    <t>D_24</t>
+  </si>
+  <si>
+    <t>WNDTRBN</t>
+  </si>
+  <si>
+    <t>SOLPV</t>
+  </si>
+  <si>
+    <t>CSP</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="\Te\x\t"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -293,8 +502,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -322,6 +537,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="51"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -361,7 +582,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -379,6 +600,11 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="13">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -694,17 +920,2560 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E39CA8-E622-4EC6-B5A7-6B0C4E956FF0}">
+  <dimension ref="B3:O150"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
+    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+    </row>
+    <row r="6" spans="2:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7">
+        <v>2030</v>
+      </c>
+      <c r="G7" s="13">
+        <v>3.3051976250754521E-3</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8">
+        <v>2030</v>
+      </c>
+      <c r="G8" s="13">
+        <v>3.1618331753269246E-3</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B9" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9">
+        <v>2030</v>
+      </c>
+      <c r="G9" s="13">
+        <v>2.8979409360310663E-3</v>
+      </c>
+      <c r="I9" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B10" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10">
+        <v>2030</v>
+      </c>
+      <c r="G10">
+        <v>2.7156926103261707E-3</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11">
+        <v>2030</v>
+      </c>
+      <c r="G11" s="13">
+        <v>2.5452192095824343E-3</v>
+      </c>
+      <c r="I11" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12">
+        <v>2030</v>
+      </c>
+      <c r="G12" s="13">
+        <v>2.5834450529081338E-3</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13">
+        <v>2030</v>
+      </c>
+      <c r="G13" s="13">
+        <v>2.7432881310744317E-3</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B14" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E14">
+        <v>2030</v>
+      </c>
+      <c r="G14" s="13">
+        <v>2.8314721319216154E-3</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B15" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15">
+        <v>2030</v>
+      </c>
+      <c r="G15">
+        <v>2.8141143326017269E-3</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16">
+        <v>2030</v>
+      </c>
+      <c r="G16">
+        <v>2.6656478128544076E-3</v>
+      </c>
+      <c r="I16" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17">
+        <v>2030</v>
+      </c>
+      <c r="G17">
+        <v>2.4530677112863486E-3</v>
+      </c>
+      <c r="I17" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <v>2030</v>
+      </c>
+      <c r="G18">
+        <v>2.1363241345921055E-3</v>
+      </c>
+      <c r="I18" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D19" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19">
+        <v>2030</v>
+      </c>
+      <c r="G19">
+        <v>1.8660639529435976E-3</v>
+      </c>
+      <c r="I19" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20">
+        <v>2030</v>
+      </c>
+      <c r="G20">
+        <v>1.7487528282965712E-3</v>
+      </c>
+      <c r="I20" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B21" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21">
+        <v>2030</v>
+      </c>
+      <c r="G21">
+        <v>1.6637860863902745E-3</v>
+      </c>
+      <c r="I21" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22">
+        <v>2030</v>
+      </c>
+      <c r="G22">
+        <v>1.8211742012316831E-3</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B23" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23">
+        <v>2030</v>
+      </c>
+      <c r="G23">
+        <v>1.9153018835258307E-3</v>
+      </c>
+      <c r="I23" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>2030</v>
+      </c>
+      <c r="G24">
+        <v>1.9744590518638132E-3</v>
+      </c>
+      <c r="I24" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B25" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25">
+        <v>2030</v>
+      </c>
+      <c r="G25">
+        <v>2.1878436160058393E-3</v>
+      </c>
+      <c r="I25" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>2030</v>
+      </c>
+      <c r="G26">
+        <v>2.3889741533883327E-3</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B27" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>23</v>
+      </c>
+      <c r="E27">
+        <v>2030</v>
+      </c>
+      <c r="G27">
+        <v>2.4063426997311056E-3</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" t="s">
+        <v>23</v>
+      </c>
+      <c r="E28">
+        <v>2030</v>
+      </c>
+      <c r="G28">
+        <v>2.5925256698099051E-3</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E29">
+        <v>2030</v>
+      </c>
+      <c r="G29">
+        <v>2.9724559200622644E-3</v>
+      </c>
+      <c r="I29" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E30">
+        <v>2030</v>
+      </c>
+      <c r="G30">
+        <v>3.3823091606694387E-3</v>
+      </c>
+      <c r="I30" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31">
+        <v>2030</v>
+      </c>
+      <c r="G31">
+        <v>3.3051976250754521E-3</v>
+      </c>
+      <c r="I31" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D32" t="s">
+        <v>23</v>
+      </c>
+      <c r="E32">
+        <v>2030</v>
+      </c>
+      <c r="G32">
+        <v>3.1618331753269246E-3</v>
+      </c>
+      <c r="I32" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E33">
+        <v>2030</v>
+      </c>
+      <c r="G33">
+        <v>2.8979409360310663E-3</v>
+      </c>
+      <c r="I33" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E34">
+        <v>2030</v>
+      </c>
+      <c r="G34">
+        <v>2.7156926103261707E-3</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>23</v>
+      </c>
+      <c r="E35">
+        <v>2030</v>
+      </c>
+      <c r="G35">
+        <v>2.5452192095824343E-3</v>
+      </c>
+      <c r="I35" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D36" t="s">
+        <v>23</v>
+      </c>
+      <c r="E36">
+        <v>2030</v>
+      </c>
+      <c r="G36">
+        <v>2.5834450529081338E-3</v>
+      </c>
+      <c r="I36" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D37" t="s">
+        <v>23</v>
+      </c>
+      <c r="E37">
+        <v>2030</v>
+      </c>
+      <c r="G37">
+        <v>2.7432881310744317E-3</v>
+      </c>
+      <c r="I37" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D38" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38">
+        <v>2030</v>
+      </c>
+      <c r="G38">
+        <v>2.8314721319216154E-3</v>
+      </c>
+      <c r="I38" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>23</v>
+      </c>
+      <c r="E39">
+        <v>2030</v>
+      </c>
+      <c r="G39">
+        <v>2.8141143326017269E-3</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40">
+        <v>2030</v>
+      </c>
+      <c r="G40">
+        <v>2.6656478128544076E-3</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B41" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41">
+        <v>2030</v>
+      </c>
+      <c r="G41">
+        <v>2.4530677112863486E-3</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42">
+        <v>2030</v>
+      </c>
+      <c r="G42">
+        <v>2.1363241345921055E-3</v>
+      </c>
+      <c r="I42" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B43" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43">
+        <v>2030</v>
+      </c>
+      <c r="G43">
+        <v>1.8660639529435976E-3</v>
+      </c>
+      <c r="I43" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44">
+        <v>2030</v>
+      </c>
+      <c r="G44">
+        <v>1.7487528282965712E-3</v>
+      </c>
+      <c r="I44" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45">
+        <v>2030</v>
+      </c>
+      <c r="G45">
+        <v>1.6637860863902745E-3</v>
+      </c>
+      <c r="I45" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46">
+        <v>2030</v>
+      </c>
+      <c r="G46">
+        <v>1.8211742012316831E-3</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B47" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47">
+        <v>2030</v>
+      </c>
+      <c r="G47">
+        <v>1.9153018835258307E-3</v>
+      </c>
+      <c r="I47" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48">
+        <v>2030</v>
+      </c>
+      <c r="G48">
+        <v>1.9744590518638132E-3</v>
+      </c>
+      <c r="I48" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B49" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49">
+        <v>2030</v>
+      </c>
+      <c r="G49">
+        <v>2.1878436160058393E-3</v>
+      </c>
+      <c r="I49" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B50" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" t="s">
+        <v>23</v>
+      </c>
+      <c r="E50">
+        <v>2030</v>
+      </c>
+      <c r="G50">
+        <v>2.3889741533883327E-3</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B51" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51">
+        <v>2030</v>
+      </c>
+      <c r="G51">
+        <v>2.4063426997311056E-3</v>
+      </c>
+      <c r="I51" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B52" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D52" t="s">
+        <v>23</v>
+      </c>
+      <c r="E52">
+        <v>2030</v>
+      </c>
+      <c r="G52">
+        <v>2.5925256698099051E-3</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B53" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D53" t="s">
+        <v>23</v>
+      </c>
+      <c r="E53">
+        <v>2030</v>
+      </c>
+      <c r="G53">
+        <v>2.9724559200622644E-3</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D54" t="s">
+        <v>23</v>
+      </c>
+      <c r="E54">
+        <v>2030</v>
+      </c>
+      <c r="G54">
+        <v>3.3823091606694387E-3</v>
+      </c>
+      <c r="I54" s="12" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="55" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B55" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" t="s">
+        <v>23</v>
+      </c>
+      <c r="E55">
+        <v>2030</v>
+      </c>
+      <c r="G55" s="16">
+        <v>0</v>
+      </c>
+      <c r="I55" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B56" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>23</v>
+      </c>
+      <c r="E56">
+        <v>2030</v>
+      </c>
+      <c r="G56" s="16">
+        <v>0</v>
+      </c>
+      <c r="I56" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B57" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D57" t="s">
+        <v>23</v>
+      </c>
+      <c r="E57">
+        <v>2030</v>
+      </c>
+      <c r="G57" s="17">
+        <v>0</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B58" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D58" t="s">
+        <v>23</v>
+      </c>
+      <c r="E58">
+        <v>2030</v>
+      </c>
+      <c r="G58" s="17">
+        <v>0</v>
+      </c>
+      <c r="I58" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B59" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D59" t="s">
+        <v>23</v>
+      </c>
+      <c r="E59">
+        <v>2030</v>
+      </c>
+      <c r="G59" s="17">
+        <v>0</v>
+      </c>
+      <c r="I59" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D60" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60">
+        <v>2030</v>
+      </c>
+      <c r="G60" s="17">
+        <v>0</v>
+      </c>
+      <c r="I60" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B61" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D61" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61">
+        <v>2030</v>
+      </c>
+      <c r="G61" s="17">
+        <v>6.9165519713261618E-3</v>
+      </c>
+      <c r="I61" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B62" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D62" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62">
+        <v>2030</v>
+      </c>
+      <c r="G62" s="17">
+        <v>4.9742853046594968E-2</v>
+      </c>
+      <c r="I62" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B63" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" t="s">
+        <v>23</v>
+      </c>
+      <c r="E63">
+        <v>2030</v>
+      </c>
+      <c r="G63" s="17">
+        <v>0.12554577777777776</v>
+      </c>
+      <c r="I63" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B64" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D64" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64">
+        <v>2030</v>
+      </c>
+      <c r="G64" s="17">
+        <v>0.2058007025089606</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B65" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" t="s">
+        <v>23</v>
+      </c>
+      <c r="E65">
+        <v>2030</v>
+      </c>
+      <c r="G65" s="17">
+        <v>0.27468446594982077</v>
+      </c>
+      <c r="I65" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B66" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D66" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66">
+        <v>2030</v>
+      </c>
+      <c r="G66" s="17">
+        <v>0.32637437275985665</v>
+      </c>
+      <c r="I66" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B67" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D67" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67">
+        <v>2030</v>
+      </c>
+      <c r="G67" s="17">
+        <v>0.35267560573476697</v>
+      </c>
+      <c r="I67" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D68" t="s">
+        <v>23</v>
+      </c>
+      <c r="E68">
+        <v>2030</v>
+      </c>
+      <c r="G68" s="17">
+        <v>0.34322033691756271</v>
+      </c>
+      <c r="I68" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B69" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E69">
+        <v>2030</v>
+      </c>
+      <c r="G69" s="17">
+        <v>0.30308891039426522</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B70" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" t="s">
+        <v>23</v>
+      </c>
+      <c r="E70">
+        <v>2030</v>
+      </c>
+      <c r="G70" s="17">
+        <v>0.23170381362007167</v>
+      </c>
+      <c r="I70" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B71" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D71" t="s">
+        <v>23</v>
+      </c>
+      <c r="E71">
+        <v>2030</v>
+      </c>
+      <c r="G71" s="17">
+        <v>0.14172651612903225</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B72" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D72" t="s">
+        <v>23</v>
+      </c>
+      <c r="E72">
+        <v>2030</v>
+      </c>
+      <c r="G72" s="16">
+        <v>5.3895483870967743E-2</v>
+      </c>
+      <c r="I72" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B73" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D73" t="s">
+        <v>23</v>
+      </c>
+      <c r="E73">
+        <v>2030</v>
+      </c>
+      <c r="G73" s="16">
+        <v>2.6301935483870969E-3</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D74" t="s">
+        <v>23</v>
+      </c>
+      <c r="E74">
+        <v>2030</v>
+      </c>
+      <c r="G74" s="16">
+        <v>0</v>
+      </c>
+      <c r="I74" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B75" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D75" t="s">
+        <v>23</v>
+      </c>
+      <c r="E75">
+        <v>2030</v>
+      </c>
+      <c r="G75" s="16">
+        <v>0</v>
+      </c>
+      <c r="I75" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D76" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76">
+        <v>2030</v>
+      </c>
+      <c r="G76" s="16">
+        <v>0</v>
+      </c>
+      <c r="I76" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B77" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D77" t="s">
+        <v>23</v>
+      </c>
+      <c r="E77">
+        <v>2030</v>
+      </c>
+      <c r="G77" s="16">
+        <v>0</v>
+      </c>
+      <c r="I77" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B78" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D78" t="s">
+        <v>23</v>
+      </c>
+      <c r="E78">
+        <v>2030</v>
+      </c>
+      <c r="G78" s="16">
+        <v>0</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B79" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E79">
+        <v>2030</v>
+      </c>
+      <c r="G79" s="16">
+        <v>0</v>
+      </c>
+      <c r="I79" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B80" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D80" t="s">
+        <v>23</v>
+      </c>
+      <c r="E80">
+        <v>2030</v>
+      </c>
+      <c r="G80" s="16">
+        <v>0</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B81" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D81" t="s">
+        <v>23</v>
+      </c>
+      <c r="E81">
+        <v>2030</v>
+      </c>
+      <c r="G81" s="16">
+        <v>0</v>
+      </c>
+      <c r="I81" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B82" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D82" t="s">
+        <v>23</v>
+      </c>
+      <c r="E82">
+        <v>2030</v>
+      </c>
+      <c r="G82" s="16">
+        <v>0</v>
+      </c>
+      <c r="I82" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B83" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D83" t="s">
+        <v>23</v>
+      </c>
+      <c r="E83">
+        <v>2030</v>
+      </c>
+      <c r="G83" s="16">
+        <v>0</v>
+      </c>
+      <c r="I83" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B84" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D84" t="s">
+        <v>23</v>
+      </c>
+      <c r="E84">
+        <v>2030</v>
+      </c>
+      <c r="G84" s="16">
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B85" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D85" t="s">
+        <v>23</v>
+      </c>
+      <c r="E85">
+        <v>2030</v>
+      </c>
+      <c r="G85" s="16">
+        <v>6.4190919952210254E-3</v>
+      </c>
+      <c r="I85" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B86" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D86" t="s">
+        <v>23</v>
+      </c>
+      <c r="E86">
+        <v>2030</v>
+      </c>
+      <c r="G86" s="16">
+        <v>7.0838474313022717E-2</v>
+      </c>
+      <c r="I86" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B87" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D87" t="s">
+        <v>23</v>
+      </c>
+      <c r="E87">
+        <v>2030</v>
+      </c>
+      <c r="G87" s="16">
+        <v>0.15999428793309439</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B88" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88" t="s">
+        <v>23</v>
+      </c>
+      <c r="E88">
+        <v>2030</v>
+      </c>
+      <c r="G88" s="16">
+        <v>0.25343209199522099</v>
+      </c>
+      <c r="I88" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B89" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D89" t="s">
+        <v>23</v>
+      </c>
+      <c r="E89">
+        <v>2030</v>
+      </c>
+      <c r="G89" s="16">
+        <v>0.32960197968936678</v>
+      </c>
+      <c r="I89" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B90" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D90" t="s">
+        <v>23</v>
+      </c>
+      <c r="E90">
+        <v>2030</v>
+      </c>
+      <c r="G90" s="16">
+        <v>0.37592762246117079</v>
+      </c>
+      <c r="I90" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B91" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D91" t="s">
+        <v>23</v>
+      </c>
+      <c r="E91">
+        <v>2030</v>
+      </c>
+      <c r="G91" s="16">
+        <v>0.38776096057347664</v>
+      </c>
+      <c r="I91" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B92" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D92" t="s">
+        <v>23</v>
+      </c>
+      <c r="E92">
+        <v>2030</v>
+      </c>
+      <c r="G92" s="16">
+        <v>0.36426783751493425</v>
+      </c>
+      <c r="I92" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B93" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D93" t="s">
+        <v>23</v>
+      </c>
+      <c r="E93">
+        <v>2030</v>
+      </c>
+      <c r="G93" s="16">
+        <v>0.31009156033452806</v>
+      </c>
+      <c r="I93" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B94" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D94" t="s">
+        <v>23</v>
+      </c>
+      <c r="E94">
+        <v>2030</v>
+      </c>
+      <c r="G94" s="16">
+        <v>0.23188419952210276</v>
+      </c>
+      <c r="I94" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B95" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D95" t="s">
+        <v>23</v>
+      </c>
+      <c r="E95">
+        <v>2030</v>
+      </c>
+      <c r="G95" s="16">
+        <v>0.13618056033452808</v>
+      </c>
+      <c r="I95" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B96" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D96" t="s">
+        <v>23</v>
+      </c>
+      <c r="E96">
+        <v>2030</v>
+      </c>
+      <c r="G96" s="16">
+        <v>4.9357593787335743E-2</v>
+      </c>
+      <c r="I96" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B97" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D97" t="s">
+        <v>23</v>
+      </c>
+      <c r="E97">
+        <v>2030</v>
+      </c>
+      <c r="G97" s="16">
+        <v>7.5268817204301086E-6</v>
+      </c>
+      <c r="I97" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B98" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D98" t="s">
+        <v>23</v>
+      </c>
+      <c r="E98">
+        <v>2030</v>
+      </c>
+      <c r="G98" s="16">
+        <v>0</v>
+      </c>
+      <c r="I98" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B99" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D99" t="s">
+        <v>23</v>
+      </c>
+      <c r="E99">
+        <v>2030</v>
+      </c>
+      <c r="G99" s="16">
+        <v>0</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B100" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100">
+        <v>2030</v>
+      </c>
+      <c r="G100" s="16">
+        <v>0</v>
+      </c>
+      <c r="I100" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B101" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D101" t="s">
+        <v>23</v>
+      </c>
+      <c r="E101">
+        <v>2030</v>
+      </c>
+      <c r="G101" s="16">
+        <v>0</v>
+      </c>
+      <c r="I101" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B102" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D102" t="s">
+        <v>23</v>
+      </c>
+      <c r="E102">
+        <v>2030</v>
+      </c>
+      <c r="G102" s="17">
+        <v>0</v>
+      </c>
+      <c r="I102" s="12" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B103" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103">
+        <v>2030</v>
+      </c>
+      <c r="G103" s="16">
+        <v>1</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="104" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B104" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104">
+        <v>2030</v>
+      </c>
+      <c r="G104" s="16">
+        <v>1</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B105" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D105" t="s">
+        <v>23</v>
+      </c>
+      <c r="E105">
+        <v>2030</v>
+      </c>
+      <c r="G105" s="16">
+        <v>1</v>
+      </c>
+      <c r="I105" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="106" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B106" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="D106" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106">
+        <v>2030</v>
+      </c>
+      <c r="G106" s="16">
+        <v>1</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B107" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="D107" t="s">
+        <v>23</v>
+      </c>
+      <c r="E107">
+        <v>2030</v>
+      </c>
+      <c r="G107" s="16">
+        <v>1</v>
+      </c>
+      <c r="I107" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B108" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D108" t="s">
+        <v>23</v>
+      </c>
+      <c r="E108">
+        <v>2030</v>
+      </c>
+      <c r="G108" s="16">
+        <v>1</v>
+      </c>
+      <c r="I108" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B109" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D109" t="s">
+        <v>23</v>
+      </c>
+      <c r="E109">
+        <v>2030</v>
+      </c>
+      <c r="G109" s="16">
+        <v>1</v>
+      </c>
+      <c r="I109" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B110" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D110" t="s">
+        <v>23</v>
+      </c>
+      <c r="E110">
+        <v>2030</v>
+      </c>
+      <c r="G110" s="16">
+        <v>1</v>
+      </c>
+      <c r="I110" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B111" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D111" t="s">
+        <v>23</v>
+      </c>
+      <c r="E111">
+        <v>2030</v>
+      </c>
+      <c r="G111" s="16">
+        <v>1</v>
+      </c>
+      <c r="I111" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B112" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D112" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112">
+        <v>2030</v>
+      </c>
+      <c r="G112" s="16">
+        <v>1</v>
+      </c>
+      <c r="I112" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="113" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B113" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D113" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113">
+        <v>2030</v>
+      </c>
+      <c r="G113" s="16">
+        <v>1</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="114" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B114" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D114" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114">
+        <v>2030</v>
+      </c>
+      <c r="G114" s="16">
+        <v>1</v>
+      </c>
+      <c r="I114" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="115" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B115" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D115" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115">
+        <v>2030</v>
+      </c>
+      <c r="G115" s="16">
+        <v>1</v>
+      </c>
+      <c r="I115" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="116" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B116" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="D116" t="s">
+        <v>23</v>
+      </c>
+      <c r="E116">
+        <v>2030</v>
+      </c>
+      <c r="G116" s="16">
+        <v>1</v>
+      </c>
+      <c r="I116" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="117" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B117" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D117" t="s">
+        <v>23</v>
+      </c>
+      <c r="E117">
+        <v>2030</v>
+      </c>
+      <c r="G117" s="16">
+        <v>1</v>
+      </c>
+      <c r="I117" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="118" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B118" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D118" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118">
+        <v>2030</v>
+      </c>
+      <c r="G118" s="16">
+        <v>1</v>
+      </c>
+      <c r="I118" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="119" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B119" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="D119" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119">
+        <v>2030</v>
+      </c>
+      <c r="G119" s="16">
+        <v>1</v>
+      </c>
+      <c r="I119" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="120" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B120" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="D120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120">
+        <v>2030</v>
+      </c>
+      <c r="G120" s="16">
+        <v>1</v>
+      </c>
+      <c r="I120" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="121" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B121" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D121" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121">
+        <v>2030</v>
+      </c>
+      <c r="G121" s="16">
+        <v>1</v>
+      </c>
+      <c r="I121" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="122" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B122" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D122" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122">
+        <v>2030</v>
+      </c>
+      <c r="G122" s="16">
+        <v>1</v>
+      </c>
+      <c r="I122" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="123" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B123" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D123" t="s">
+        <v>23</v>
+      </c>
+      <c r="E123">
+        <v>2030</v>
+      </c>
+      <c r="G123" s="16">
+        <v>1</v>
+      </c>
+      <c r="I123" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="124" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B124" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D124" t="s">
+        <v>23</v>
+      </c>
+      <c r="E124">
+        <v>2030</v>
+      </c>
+      <c r="G124" s="16">
+        <v>1</v>
+      </c>
+      <c r="I124" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="125" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B125" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D125" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125">
+        <v>2030</v>
+      </c>
+      <c r="G125" s="16">
+        <v>1</v>
+      </c>
+      <c r="I125" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="126" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B126" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D126" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126">
+        <v>2030</v>
+      </c>
+      <c r="G126" s="16">
+        <v>1</v>
+      </c>
+      <c r="I126" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B127" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D127" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127">
+        <v>2030</v>
+      </c>
+      <c r="G127" s="16">
+        <v>1</v>
+      </c>
+      <c r="I127" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B128" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D128" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128">
+        <v>2030</v>
+      </c>
+      <c r="G128" s="16">
+        <v>1</v>
+      </c>
+      <c r="I128" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="129" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B129" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="D129" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129">
+        <v>2030</v>
+      </c>
+      <c r="G129" s="16">
+        <v>1</v>
+      </c>
+      <c r="I129" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="130" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B130" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D130" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130">
+        <v>2030</v>
+      </c>
+      <c r="G130" s="16">
+        <v>1</v>
+      </c>
+      <c r="I130" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="131" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B131" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D131" t="s">
+        <v>23</v>
+      </c>
+      <c r="E131">
+        <v>2030</v>
+      </c>
+      <c r="G131" s="16">
+        <v>1</v>
+      </c>
+      <c r="I131" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="132" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B132" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="D132" t="s">
+        <v>23</v>
+      </c>
+      <c r="E132">
+        <v>2030</v>
+      </c>
+      <c r="G132" s="16">
+        <v>1</v>
+      </c>
+      <c r="I132" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="133" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B133" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D133" t="s">
+        <v>23</v>
+      </c>
+      <c r="E133">
+        <v>2030</v>
+      </c>
+      <c r="G133" s="16">
+        <v>1</v>
+      </c>
+      <c r="I133" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="134" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B134" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="D134" t="s">
+        <v>23</v>
+      </c>
+      <c r="E134">
+        <v>2030</v>
+      </c>
+      <c r="G134" s="16">
+        <v>1</v>
+      </c>
+      <c r="I134" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="135" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B135" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="D135" t="s">
+        <v>23</v>
+      </c>
+      <c r="E135">
+        <v>2030</v>
+      </c>
+      <c r="G135" s="16">
+        <v>1</v>
+      </c>
+      <c r="I135" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="136" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B136" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="D136" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136">
+        <v>2030</v>
+      </c>
+      <c r="G136" s="16">
+        <v>1</v>
+      </c>
+      <c r="I136" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="137" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B137" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D137" t="s">
+        <v>23</v>
+      </c>
+      <c r="E137">
+        <v>2030</v>
+      </c>
+      <c r="G137" s="16">
+        <v>1</v>
+      </c>
+      <c r="I137" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="138" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B138" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="D138" t="s">
+        <v>23</v>
+      </c>
+      <c r="E138">
+        <v>2030</v>
+      </c>
+      <c r="G138" s="16">
+        <v>1</v>
+      </c>
+      <c r="I138" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="139" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B139" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D139" t="s">
+        <v>23</v>
+      </c>
+      <c r="E139">
+        <v>2030</v>
+      </c>
+      <c r="G139" s="16">
+        <v>1</v>
+      </c>
+      <c r="I139" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="140" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B140" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D140" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140">
+        <v>2030</v>
+      </c>
+      <c r="G140" s="16">
+        <v>1</v>
+      </c>
+      <c r="I140" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="141" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B141" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D141" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141">
+        <v>2030</v>
+      </c>
+      <c r="G141" s="16">
+        <v>1</v>
+      </c>
+      <c r="I141" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="142" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B142" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D142" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142">
+        <v>2030</v>
+      </c>
+      <c r="G142" s="16">
+        <v>1</v>
+      </c>
+      <c r="I142" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="143" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B143" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D143" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143">
+        <v>2030</v>
+      </c>
+      <c r="G143" s="16">
+        <v>1</v>
+      </c>
+      <c r="I143" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="144" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B144" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D144" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144">
+        <v>2030</v>
+      </c>
+      <c r="G144" s="16">
+        <v>1</v>
+      </c>
+      <c r="I144" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="145" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B145" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D145" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145">
+        <v>2030</v>
+      </c>
+      <c r="G145" s="16">
+        <v>1</v>
+      </c>
+      <c r="I145" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="146" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B146" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D146" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146">
+        <v>2030</v>
+      </c>
+      <c r="G146" s="16">
+        <v>1</v>
+      </c>
+      <c r="I146" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="147" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B147" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D147" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147">
+        <v>2030</v>
+      </c>
+      <c r="G147" s="16">
+        <v>1</v>
+      </c>
+      <c r="I147" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="148" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B148" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D148" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148">
+        <v>2030</v>
+      </c>
+      <c r="G148" s="16">
+        <v>1</v>
+      </c>
+      <c r="I148" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="149" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B149" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D149" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149">
+        <v>2030</v>
+      </c>
+      <c r="G149" s="16">
+        <v>1</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B150" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D150" t="s">
+        <v>23</v>
+      </c>
+      <c r="E150">
+        <v>2030</v>
+      </c>
+      <c r="G150" s="16">
+        <v>1</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:O4"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.7109375" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.6640625" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
@@ -717,7 +3486,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:15" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
@@ -767,38 +3536,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="B3:O14"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
-    <col min="3" max="4" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.109375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.85546875" customWidth="1"/>
-    <col min="17" max="17" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.88671875" customWidth="1"/>
+    <col min="17" max="17" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:15" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:15" ht="15" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
@@ -811,7 +3580,7 @@
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
     </row>
-    <row r="6" spans="2:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" ht="22.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
@@ -855,7 +3624,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="E7" s="8"/>
@@ -869,7 +3638,7 @@
       <c r="N7" s="8"/>
       <c r="O7" s="8"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>0</v>
       </c>
@@ -882,7 +3651,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:15" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
         <v>2</v>
       </c>
@@ -935,32 +3704,32 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:M3"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.5703125" customWidth="1"/>
-    <col min="2" max="2" width="26.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.7109375" customWidth="1"/>
-    <col min="12" max="12" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.6640625" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
         <v>17</v>
       </c>

--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F49453C-6939-45D7-9100-50B952CAF692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD4BBEE-A867-4C23-8550-CFA578D40178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -921,7 +921,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E39CA8-E622-4EC6-B5A7-6B0C4E956FF0}">
-  <dimension ref="B3:O150"/>
+  <dimension ref="B3:O152"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -2639,42 +2639,18 @@
       </c>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D103" t="s">
-        <v>23</v>
-      </c>
-      <c r="E103">
-        <v>2030</v>
-      </c>
-      <c r="G103" s="16">
-        <v>1</v>
-      </c>
-      <c r="I103" s="12" t="s">
-        <v>74</v>
-      </c>
+      <c r="B103" s="15"/>
+      <c r="G103" s="17"/>
+      <c r="I103" s="12"/>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D104" t="s">
-        <v>23</v>
-      </c>
-      <c r="E104">
-        <v>2030</v>
-      </c>
-      <c r="G104" s="16">
-        <v>1</v>
-      </c>
-      <c r="I104" s="12" t="s">
-        <v>74</v>
-      </c>
+      <c r="B104" s="15"/>
+      <c r="G104" s="17"/>
+      <c r="I104" s="12"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="14" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D105" t="s">
         <v>23</v>
@@ -2691,7 +2667,7 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="14" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D106" t="s">
         <v>23</v>
@@ -2708,7 +2684,7 @@
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" s="14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D107" t="s">
         <v>23</v>
@@ -2725,7 +2701,7 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D108" t="s">
         <v>23</v>
@@ -2742,7 +2718,7 @@
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D109" t="s">
         <v>23</v>
@@ -2759,7 +2735,7 @@
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D110" t="s">
         <v>23</v>
@@ -2776,7 +2752,7 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D111" t="s">
         <v>23</v>
@@ -2793,7 +2769,7 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="14" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D112" t="s">
         <v>23</v>
@@ -2810,7 +2786,7 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D113" t="s">
         <v>23</v>
@@ -2827,7 +2803,7 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" s="14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D114" t="s">
         <v>23</v>
@@ -2844,7 +2820,7 @@
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" s="14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D115" t="s">
         <v>23</v>
@@ -2861,7 +2837,7 @@
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" s="14" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -2878,7 +2854,7 @@
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="14" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s">
         <v>23</v>
@@ -2895,7 +2871,7 @@
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D118" t="s">
         <v>23</v>
@@ -2912,7 +2888,7 @@
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D119" t="s">
         <v>23</v>
@@ -2929,7 +2905,7 @@
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D120" t="s">
         <v>23</v>
@@ -2946,7 +2922,7 @@
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D121" t="s">
         <v>23</v>
@@ -2963,7 +2939,7 @@
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" s="14" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D122" t="s">
         <v>23</v>
@@ -2980,7 +2956,7 @@
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="14" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D123" t="s">
         <v>23</v>
@@ -2997,7 +2973,7 @@
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D124" t="s">
         <v>23</v>
@@ -3014,7 +2990,7 @@
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" s="14" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D125" t="s">
         <v>23</v>
@@ -3031,7 +3007,7 @@
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D126" t="s">
         <v>23</v>
@@ -3048,7 +3024,7 @@
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" s="14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D127" t="s">
         <v>23</v>
@@ -3065,7 +3041,7 @@
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" s="14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D128" t="s">
         <v>23</v>
@@ -3082,7 +3058,7 @@
     </row>
     <row r="129" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B129" s="14" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D129" t="s">
         <v>23</v>
@@ -3099,7 +3075,7 @@
     </row>
     <row r="130" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B130" s="14" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D130" t="s">
         <v>23</v>
@@ -3116,7 +3092,7 @@
     </row>
     <row r="131" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B131" s="14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D131" t="s">
         <v>23</v>
@@ -3133,7 +3109,7 @@
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B132" s="14" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D132" t="s">
         <v>23</v>
@@ -3150,7 +3126,7 @@
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B133" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D133" t="s">
         <v>23</v>
@@ -3167,7 +3143,7 @@
     </row>
     <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B134" s="14" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D134" t="s">
         <v>23</v>
@@ -3184,7 +3160,7 @@
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B135" s="14" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D135" t="s">
         <v>23</v>
@@ -3201,7 +3177,7 @@
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B136" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D136" t="s">
         <v>23</v>
@@ -3218,7 +3194,7 @@
     </row>
     <row r="137" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B137" s="14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D137" t="s">
         <v>23</v>
@@ -3235,7 +3211,7 @@
     </row>
     <row r="138" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B138" s="14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D138" t="s">
         <v>23</v>
@@ -3252,7 +3228,7 @@
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B139" s="14" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D139" t="s">
         <v>23</v>
@@ -3269,7 +3245,7 @@
     </row>
     <row r="140" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B140" s="14" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D140" t="s">
         <v>23</v>
@@ -3286,7 +3262,7 @@
     </row>
     <row r="141" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B141" s="14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D141" t="s">
         <v>23</v>
@@ -3303,7 +3279,7 @@
     </row>
     <row r="142" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B142" s="14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D142" t="s">
         <v>23</v>
@@ -3320,7 +3296,7 @@
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B143" s="14" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D143" t="s">
         <v>23</v>
@@ -3337,7 +3313,7 @@
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B144" s="14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D144" t="s">
         <v>23</v>
@@ -3354,7 +3330,7 @@
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B145" s="14" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D145" t="s">
         <v>23</v>
@@ -3371,7 +3347,7 @@
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B146" s="14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D146" t="s">
         <v>23</v>
@@ -3388,7 +3364,7 @@
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B147" s="14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D147" t="s">
         <v>23</v>
@@ -3405,7 +3381,7 @@
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B148" s="14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D148" t="s">
         <v>23</v>
@@ -3422,35 +3398,69 @@
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B149" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D149" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149">
+        <v>2030</v>
+      </c>
+      <c r="G149" s="16">
+        <v>1</v>
+      </c>
+      <c r="I149" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B150" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D150" t="s">
+        <v>23</v>
+      </c>
+      <c r="E150">
+        <v>2030</v>
+      </c>
+      <c r="G150" s="16">
+        <v>1</v>
+      </c>
+      <c r="I150" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B151" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D149" t="s">
-        <v>23</v>
-      </c>
-      <c r="E149">
-        <v>2030</v>
-      </c>
-      <c r="G149" s="16">
-        <v>1</v>
-      </c>
-      <c r="I149" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B150" s="15" t="s">
+      <c r="D151" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151">
+        <v>2030</v>
+      </c>
+      <c r="G151" s="16">
+        <v>1</v>
+      </c>
+      <c r="I151" s="12" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B152" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="D150" t="s">
-        <v>23</v>
-      </c>
-      <c r="E150">
-        <v>2030</v>
-      </c>
-      <c r="G150" s="16">
-        <v>1</v>
-      </c>
-      <c r="I150" s="12" t="s">
+      <c r="D152" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152">
+        <v>2030</v>
+      </c>
+      <c r="G152" s="16">
+        <v>1</v>
+      </c>
+      <c r="I152" s="12" t="s">
         <v>74</v>
       </c>
     </row>

--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD4BBEE-A867-4C23-8550-CFA578D40178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A01E62-5CAA-4237-8074-2C1FFAEC953B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,20 @@
     <sheet name="Trans Tables" sheetId="17" r:id="rId3"/>
     <sheet name="FILL Table" sheetId="19" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -921,7 +934,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E39CA8-E622-4EC6-B5A7-6B0C4E956FF0}">
-  <dimension ref="B3:O152"/>
+  <dimension ref="B3:O150"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.88671875" customWidth="1"/>
@@ -1935,7 +1948,7 @@
         <v>2030</v>
       </c>
       <c r="G61" s="17">
-        <v>6.9165519713261618E-3</v>
+        <v>0</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>73</v>
@@ -1952,7 +1965,7 @@
         <v>2030</v>
       </c>
       <c r="G62" s="17">
-        <v>4.9742853046594968E-2</v>
+        <v>8.6215966388704365E-2</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>73</v>
@@ -1969,7 +1982,7 @@
         <v>2030</v>
       </c>
       <c r="G63" s="17">
-        <v>0.12554577777777776</v>
+        <v>0.28600141894651748</v>
       </c>
       <c r="I63" s="12" t="s">
         <v>73</v>
@@ -1986,7 +1999,7 @@
         <v>2030</v>
       </c>
       <c r="G64" s="17">
-        <v>0.2058007025089606</v>
+        <v>0.49907951813804202</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>73</v>
@@ -2003,7 +2016,7 @@
         <v>2030</v>
       </c>
       <c r="G65" s="17">
-        <v>0.27468446594982077</v>
+        <v>0.70775777457339939</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>73</v>
@@ -2020,7 +2033,7 @@
         <v>2030</v>
       </c>
       <c r="G66" s="17">
-        <v>0.32637437275985665</v>
+        <v>0.87024932186465265</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>73</v>
@@ -2037,7 +2050,7 @@
         <v>2030</v>
       </c>
       <c r="G67" s="17">
-        <v>0.35267560573476697</v>
+        <v>0.92893717153818411</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>73</v>
@@ -2054,7 +2067,7 @@
         <v>2030</v>
       </c>
       <c r="G68" s="17">
-        <v>0.34322033691756271</v>
+        <v>0.90189792624036313</v>
       </c>
       <c r="I68" s="12" t="s">
         <v>73</v>
@@ -2071,7 +2084,7 @@
         <v>2030</v>
       </c>
       <c r="G69" s="17">
-        <v>0.30308891039426522</v>
+        <v>0.81189902626500698</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>73</v>
@@ -2088,7 +2101,7 @@
         <v>2030</v>
       </c>
       <c r="G70" s="17">
-        <v>0.23170381362007167</v>
+        <v>0.63043461206223927</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>73</v>
@@ -2105,7 +2118,7 @@
         <v>2030</v>
       </c>
       <c r="G71" s="17">
-        <v>0.14172651612903225</v>
+        <v>0.42069713422261951</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>73</v>
@@ -2122,7 +2135,7 @@
         <v>2030</v>
       </c>
       <c r="G72" s="16">
-        <v>5.3895483870967743E-2</v>
+        <v>0.20545403303996501</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>73</v>
@@ -2139,7 +2152,7 @@
         <v>2030</v>
       </c>
       <c r="G73" s="16">
-        <v>2.6301935483870969E-3</v>
+        <v>3.1380889075732013E-2</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>73</v>
@@ -2343,7 +2356,7 @@
         <v>2030</v>
       </c>
       <c r="G85" s="16">
-        <v>6.4190919952210254E-3</v>
+        <v>0</v>
       </c>
       <c r="I85" s="12" t="s">
         <v>73</v>
@@ -2360,7 +2373,7 @@
         <v>2030</v>
       </c>
       <c r="G86" s="16">
-        <v>7.0838474313022717E-2</v>
+        <v>0.12702061309745619</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>73</v>
@@ -2377,7 +2390,7 @@
         <v>2030</v>
       </c>
       <c r="G87" s="16">
-        <v>0.15999428793309439</v>
+        <v>0.36346519701100283</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>73</v>
@@ -2394,7 +2407,7 @@
         <v>2030</v>
       </c>
       <c r="G88" s="16">
-        <v>0.25343209199522099</v>
+        <v>0.61379567340694685</v>
       </c>
       <c r="I88" s="12" t="s">
         <v>73</v>
@@ -2411,7 +2424,7 @@
         <v>2030</v>
       </c>
       <c r="G89" s="16">
-        <v>0.32960197968936678</v>
+        <v>0.81192460823347123</v>
       </c>
       <c r="I89" s="12" t="s">
         <v>73</v>
@@ -2428,7 +2441,7 @@
         <v>2030</v>
       </c>
       <c r="G90" s="16">
-        <v>0.37592762246117079</v>
+        <v>0.94826524408182478</v>
       </c>
       <c r="I90" s="12" t="s">
         <v>73</v>
@@ -2445,7 +2458,7 @@
         <v>2030</v>
       </c>
       <c r="G91" s="16">
-        <v>0.38776096057347664</v>
+        <v>1</v>
       </c>
       <c r="I91" s="12" t="s">
         <v>73</v>
@@ -2462,7 +2475,7 @@
         <v>2030</v>
       </c>
       <c r="G92" s="16">
-        <v>0.36426783751493425</v>
+        <v>0.96893718006550689</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>73</v>
@@ -2479,7 +2492,7 @@
         <v>2030</v>
       </c>
       <c r="G93" s="16">
-        <v>0.31009156033452806</v>
+        <v>0.84461921666307094</v>
       </c>
       <c r="I93" s="12" t="s">
         <v>73</v>
@@ -2496,7 +2509,7 @@
         <v>2030</v>
       </c>
       <c r="G94" s="16">
-        <v>0.23188419952210276</v>
+        <v>0.65406476160589955</v>
       </c>
       <c r="I94" s="12" t="s">
         <v>73</v>
@@ -2513,7 +2526,7 @@
         <v>2030</v>
       </c>
       <c r="G95" s="16">
-        <v>0.13618056033452808</v>
+        <v>0.43068625335869931</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>73</v>
@@ -2530,7 +2543,7 @@
         <v>2030</v>
       </c>
       <c r="G96" s="16">
-        <v>4.9357593787335743E-2</v>
+        <v>0.18066958244258341</v>
       </c>
       <c r="I96" s="12" t="s">
         <v>73</v>
@@ -2547,7 +2560,7 @@
         <v>2030</v>
       </c>
       <c r="G97" s="16">
-        <v>7.5268817204301086E-6</v>
+        <v>1.3387726283170221E-2</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>73</v>
@@ -2639,18 +2652,42 @@
       </c>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B103" s="15"/>
-      <c r="G103" s="17"/>
-      <c r="I103" s="12"/>
+      <c r="B103" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103">
+        <v>2030</v>
+      </c>
+      <c r="G103" s="16">
+        <v>0</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B104" s="15"/>
-      <c r="G104" s="17"/>
-      <c r="I104" s="12"/>
+      <c r="B104" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D104" t="s">
+        <v>23</v>
+      </c>
+      <c r="E104">
+        <v>2030</v>
+      </c>
+      <c r="G104" s="16">
+        <v>0</v>
+      </c>
+      <c r="I104" s="12" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B105" s="14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D105" t="s">
         <v>23</v>
@@ -2659,7 +2696,7 @@
         <v>2030</v>
       </c>
       <c r="G105" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="12" t="s">
         <v>74</v>
@@ -2667,7 +2704,7 @@
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B106" s="14" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D106" t="s">
         <v>23</v>
@@ -2676,7 +2713,7 @@
         <v>2030</v>
       </c>
       <c r="G106" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="12" t="s">
         <v>74</v>
@@ -2684,7 +2721,7 @@
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B107" s="14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D107" t="s">
         <v>23</v>
@@ -2693,7 +2730,7 @@
         <v>2030</v>
       </c>
       <c r="G107" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" s="12" t="s">
         <v>74</v>
@@ -2701,7 +2738,7 @@
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B108" s="14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D108" t="s">
         <v>23</v>
@@ -2710,7 +2747,7 @@
         <v>2030</v>
       </c>
       <c r="G108" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="12" t="s">
         <v>74</v>
@@ -2718,7 +2755,7 @@
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B109" s="14" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D109" t="s">
         <v>23</v>
@@ -2727,7 +2764,7 @@
         <v>2030</v>
       </c>
       <c r="G109" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="12" t="s">
         <v>74</v>
@@ -2735,7 +2772,7 @@
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B110" s="14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D110" t="s">
         <v>23</v>
@@ -2744,7 +2781,7 @@
         <v>2030</v>
       </c>
       <c r="G110" s="16">
-        <v>1</v>
+        <v>0.1098256299077521</v>
       </c>
       <c r="I110" s="12" t="s">
         <v>74</v>
@@ -2752,7 +2789,7 @@
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B111" s="14" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D111" t="s">
         <v>23</v>
@@ -2761,7 +2798,7 @@
         <v>2030</v>
       </c>
       <c r="G111" s="16">
-        <v>1</v>
+        <v>0.26814642570934433</v>
       </c>
       <c r="I111" s="12" t="s">
         <v>74</v>
@@ -2769,7 +2806,7 @@
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B112" s="14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D112" t="s">
         <v>23</v>
@@ -2778,7 +2815,7 @@
         <v>2030</v>
       </c>
       <c r="G112" s="16">
-        <v>1</v>
+        <v>0.41899992403164082</v>
       </c>
       <c r="I112" s="12" t="s">
         <v>74</v>
@@ -2786,7 +2823,7 @@
     </row>
     <row r="113" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B113" s="14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D113" t="s">
         <v>23</v>
@@ -2795,7 +2832,7 @@
         <v>2030</v>
       </c>
       <c r="G113" s="16">
-        <v>1</v>
+        <v>0.57367160653674709</v>
       </c>
       <c r="I113" s="12" t="s">
         <v>74</v>
@@ -2803,7 +2840,7 @@
     </row>
     <row r="114" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B114" s="14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D114" t="s">
         <v>23</v>
@@ -2812,7 +2849,7 @@
         <v>2030</v>
       </c>
       <c r="G114" s="16">
-        <v>1</v>
+        <v>0.68228556175917943</v>
       </c>
       <c r="I114" s="12" t="s">
         <v>74</v>
@@ -2820,7 +2857,7 @@
     </row>
     <row r="115" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B115" s="14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D115" t="s">
         <v>23</v>
@@ -2829,7 +2866,7 @@
         <v>2030</v>
       </c>
       <c r="G115" s="16">
-        <v>1</v>
+        <v>0.7261312782791185</v>
       </c>
       <c r="I115" s="12" t="s">
         <v>74</v>
@@ -2837,7 +2874,7 @@
     </row>
     <row r="116" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B116" s="14" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D116" t="s">
         <v>23</v>
@@ -2846,7 +2883,7 @@
         <v>2030</v>
       </c>
       <c r="G116" s="16">
-        <v>1</v>
+        <v>0.72103097320835441</v>
       </c>
       <c r="I116" s="12" t="s">
         <v>74</v>
@@ -2854,7 +2891,7 @@
     </row>
     <row r="117" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B117" s="14" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D117" t="s">
         <v>23</v>
@@ -2863,7 +2900,7 @@
         <v>2030</v>
       </c>
       <c r="G117" s="16">
-        <v>1</v>
+        <v>0.71114032635841962</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>74</v>
@@ -2871,7 +2908,7 @@
     </row>
     <row r="118" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B118" s="14" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D118" t="s">
         <v>23</v>
@@ -2880,7 +2917,7 @@
         <v>2030</v>
       </c>
       <c r="G118" s="16">
-        <v>1</v>
+        <v>0.56075177297351309</v>
       </c>
       <c r="I118" s="12" t="s">
         <v>74</v>
@@ -2888,7 +2925,7 @@
     </row>
     <row r="119" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B119" s="14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D119" t="s">
         <v>23</v>
@@ -2897,7 +2934,7 @@
         <v>2030</v>
       </c>
       <c r="G119" s="16">
-        <v>1</v>
+        <v>0.41368828035297223</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>74</v>
@@ -2905,7 +2942,7 @@
     </row>
     <row r="120" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B120" s="14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D120" t="s">
         <v>23</v>
@@ -2914,7 +2951,7 @@
         <v>2030</v>
       </c>
       <c r="G120" s="16">
-        <v>1</v>
+        <v>0.25708637189567068</v>
       </c>
       <c r="I120" s="12" t="s">
         <v>74</v>
@@ -2922,7 +2959,7 @@
     </row>
     <row r="121" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B121" s="14" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D121" t="s">
         <v>23</v>
@@ -2931,7 +2968,7 @@
         <v>2030</v>
       </c>
       <c r="G121" s="16">
-        <v>1</v>
+        <v>3.608254498957706E-2</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>74</v>
@@ -2939,7 +2976,7 @@
     </row>
     <row r="122" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B122" s="14" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D122" t="s">
         <v>23</v>
@@ -2948,7 +2985,7 @@
         <v>2030</v>
       </c>
       <c r="G122" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" s="12" t="s">
         <v>74</v>
@@ -2956,7 +2993,7 @@
     </row>
     <row r="123" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B123" s="14" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D123" t="s">
         <v>23</v>
@@ -2965,7 +3002,7 @@
         <v>2030</v>
       </c>
       <c r="G123" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" s="12" t="s">
         <v>74</v>
@@ -2973,7 +3010,7 @@
     </row>
     <row r="124" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B124" s="14" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D124" t="s">
         <v>23</v>
@@ -2982,7 +3019,7 @@
         <v>2030</v>
       </c>
       <c r="G124" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="12" t="s">
         <v>74</v>
@@ -2990,7 +3027,7 @@
     </row>
     <row r="125" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B125" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D125" t="s">
         <v>23</v>
@@ -2999,7 +3036,7 @@
         <v>2030</v>
       </c>
       <c r="G125" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" s="12" t="s">
         <v>74</v>
@@ -3007,7 +3044,7 @@
     </row>
     <row r="126" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B126" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D126" t="s">
         <v>23</v>
@@ -3016,7 +3053,7 @@
         <v>2030</v>
       </c>
       <c r="G126" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>74</v>
@@ -3024,7 +3061,7 @@
     </row>
     <row r="127" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B127" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D127" t="s">
         <v>23</v>
@@ -3033,7 +3070,7 @@
         <v>2030</v>
       </c>
       <c r="G127" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="12" t="s">
         <v>74</v>
@@ -3041,7 +3078,7 @@
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B128" s="14" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D128" t="s">
         <v>23</v>
@@ -3050,7 +3087,7 @@
         <v>2030</v>
       </c>
       <c r="G128" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" s="12" t="s">
         <v>74</v>
@@ -3058,7 +3095,7 @@
     </row>
     <row r="129" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B129" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D129" t="s">
         <v>23</v>
@@ -3067,7 +3104,7 @@
         <v>2030</v>
       </c>
       <c r="G129" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" s="12" t="s">
         <v>74</v>
@@ -3075,7 +3112,7 @@
     </row>
     <row r="130" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B130" s="14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D130" t="s">
         <v>23</v>
@@ -3084,7 +3121,7 @@
         <v>2030</v>
       </c>
       <c r="G130" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" s="12" t="s">
         <v>74</v>
@@ -3092,7 +3129,7 @@
     </row>
     <row r="131" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B131" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D131" t="s">
         <v>23</v>
@@ -3101,7 +3138,7 @@
         <v>2030</v>
       </c>
       <c r="G131" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="12" t="s">
         <v>74</v>
@@ -3109,7 +3146,7 @@
     </row>
     <row r="132" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B132" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D132" t="s">
         <v>23</v>
@@ -3118,7 +3155,7 @@
         <v>2030</v>
       </c>
       <c r="G132" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" s="12" t="s">
         <v>74</v>
@@ -3126,7 +3163,7 @@
     </row>
     <row r="133" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B133" s="14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D133" t="s">
         <v>23</v>
@@ -3135,7 +3172,7 @@
         <v>2030</v>
       </c>
       <c r="G133" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="12" t="s">
         <v>74</v>
@@ -3143,7 +3180,7 @@
     </row>
     <row r="134" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B134" s="14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D134" t="s">
         <v>23</v>
@@ -3152,7 +3189,7 @@
         <v>2030</v>
       </c>
       <c r="G134" s="16">
-        <v>1</v>
+        <v>0.3345361656869914</v>
       </c>
       <c r="I134" s="12" t="s">
         <v>74</v>
@@ -3160,7 +3197,7 @@
     </row>
     <row r="135" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B135" s="14" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D135" t="s">
         <v>23</v>
@@ -3169,7 +3206,7 @@
         <v>2030</v>
       </c>
       <c r="G135" s="16">
-        <v>1</v>
+        <v>0.60225815947657801</v>
       </c>
       <c r="I135" s="12" t="s">
         <v>74</v>
@@ -3177,7 +3214,7 @@
     </row>
     <row r="136" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B136" s="14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D136" t="s">
         <v>23</v>
@@ -3186,7 +3223,7 @@
         <v>2030</v>
       </c>
       <c r="G136" s="16">
-        <v>1</v>
+        <v>0.80494648978700378</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>74</v>
@@ -3194,7 +3231,7 @@
     </row>
     <row r="137" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B137" s="14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D137" t="s">
         <v>23</v>
@@ -3203,7 +3240,7 @@
         <v>2030</v>
       </c>
       <c r="G137" s="16">
-        <v>1</v>
+        <v>0.91440739931818404</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>74</v>
@@ -3211,7 +3248,7 @@
     </row>
     <row r="138" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B138" s="14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D138" t="s">
         <v>23</v>
@@ -3220,7 +3257,7 @@
         <v>2030</v>
       </c>
       <c r="G138" s="16">
-        <v>1</v>
+        <v>0.97058600093061254</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>74</v>
@@ -3228,7 +3265,7 @@
     </row>
     <row r="139" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B139" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D139" t="s">
         <v>23</v>
@@ -3237,7 +3274,7 @@
         <v>2030</v>
       </c>
       <c r="G139" s="16">
-        <v>1</v>
+        <v>0.998888962747016</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>74</v>
@@ -3245,7 +3282,7 @@
     </row>
     <row r="140" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B140" s="14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D140" t="s">
         <v>23</v>
@@ -3262,7 +3299,7 @@
     </row>
     <row r="141" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B141" s="14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D141" t="s">
         <v>23</v>
@@ -3271,7 +3308,7 @@
         <v>2030</v>
       </c>
       <c r="G141" s="16">
-        <v>1</v>
+        <v>0.94102481316531672</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>74</v>
@@ -3279,7 +3316,7 @@
     </row>
     <row r="142" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B142" s="14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D142" t="s">
         <v>23</v>
@@ -3288,7 +3325,7 @@
         <v>2030</v>
       </c>
       <c r="G142" s="16">
-        <v>1</v>
+        <v>0.84154899484364765</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>74</v>
@@ -3296,7 +3333,7 @@
     </row>
     <row r="143" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B143" s="14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D143" t="s">
         <v>23</v>
@@ -3305,7 +3342,7 @@
         <v>2030</v>
       </c>
       <c r="G143" s="16">
-        <v>1</v>
+        <v>0.72343718841102689</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>74</v>
@@ -3313,7 +3350,7 @@
     </row>
     <row r="144" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B144" s="14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D144" t="s">
         <v>23</v>
@@ -3322,7 +3359,7 @@
         <v>2030</v>
       </c>
       <c r="G144" s="16">
-        <v>1</v>
+        <v>0.46359691188619939</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>74</v>
@@ -3330,7 +3367,7 @@
     </row>
     <row r="145" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B145" s="14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D145" t="s">
         <v>23</v>
@@ -3339,7 +3376,7 @@
         <v>2030</v>
       </c>
       <c r="G145" s="16">
-        <v>1</v>
+        <v>3.8326037205503913E-2</v>
       </c>
       <c r="I145" s="12" t="s">
         <v>74</v>
@@ -3347,7 +3384,7 @@
     </row>
     <row r="146" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B146" s="14" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D146" t="s">
         <v>23</v>
@@ -3356,7 +3393,7 @@
         <v>2030</v>
       </c>
       <c r="G146" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>74</v>
@@ -3364,7 +3401,7 @@
     </row>
     <row r="147" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B147" s="14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D147" t="s">
         <v>23</v>
@@ -3373,7 +3410,7 @@
         <v>2030</v>
       </c>
       <c r="G147" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>74</v>
@@ -3381,7 +3418,7 @@
     </row>
     <row r="148" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B148" s="14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D148" t="s">
         <v>23</v>
@@ -3390,7 +3427,7 @@
         <v>2030</v>
       </c>
       <c r="G148" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>74</v>
@@ -3398,7 +3435,7 @@
     </row>
     <row r="149" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B149" s="14" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D149" t="s">
         <v>23</v>
@@ -3407,15 +3444,15 @@
         <v>2030</v>
       </c>
       <c r="G149" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="150" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B150" s="14" t="s">
-        <v>69</v>
+      <c r="B150" s="15" t="s">
+        <v>71</v>
       </c>
       <c r="D150" t="s">
         <v>23</v>
@@ -3424,43 +3461,9 @@
         <v>2030</v>
       </c>
       <c r="G150" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="151" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B151" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D151" t="s">
-        <v>23</v>
-      </c>
-      <c r="E151">
-        <v>2030</v>
-      </c>
-      <c r="G151" s="16">
-        <v>1</v>
-      </c>
-      <c r="I151" s="12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="152" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B152" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D152" t="s">
-        <v>23</v>
-      </c>
-      <c r="E152">
-        <v>2030</v>
-      </c>
-      <c r="G152" s="16">
-        <v>1</v>
-      </c>
-      <c r="I152" s="12" t="s">
         <v>74</v>
       </c>
     </row>

--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A01E62-5CAA-4237-8074-2C1FFAEC953B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C85767-19DA-4B9A-B63C-A0FAA0E7743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1965,7 +1965,7 @@
         <v>2030</v>
       </c>
       <c r="G62" s="17">
-        <v>8.6215966388704365E-2</v>
+        <v>5.604037815265784E-2</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>73</v>
@@ -1982,7 +1982,7 @@
         <v>2030</v>
       </c>
       <c r="G63" s="17">
-        <v>0.28600141894651748</v>
+        <v>0.18590092231523636</v>
       </c>
       <c r="I63" s="12" t="s">
         <v>73</v>
@@ -1999,7 +1999,7 @@
         <v>2030</v>
       </c>
       <c r="G64" s="17">
-        <v>0.49907951813804202</v>
+        <v>0.32440168678972731</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>73</v>
@@ -2016,7 +2016,7 @@
         <v>2030</v>
       </c>
       <c r="G65" s="17">
-        <v>0.70775777457339939</v>
+        <v>0.46004255347270961</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>73</v>
@@ -2033,7 +2033,7 @@
         <v>2030</v>
       </c>
       <c r="G66" s="17">
-        <v>0.87024932186465265</v>
+        <v>0.56566205921202428</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>73</v>
@@ -2050,7 +2050,7 @@
         <v>2030</v>
       </c>
       <c r="G67" s="17">
-        <v>0.92893717153818411</v>
+        <v>0.60380916149981967</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>73</v>
@@ -2067,7 +2067,7 @@
         <v>2030</v>
       </c>
       <c r="G68" s="17">
-        <v>0.90189792624036313</v>
+        <v>0.58623365205623601</v>
       </c>
       <c r="I68" s="12" t="s">
         <v>73</v>
@@ -2084,7 +2084,7 @@
         <v>2030</v>
       </c>
       <c r="G69" s="17">
-        <v>0.81189902626500698</v>
+        <v>0.52773436707225452</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>73</v>
@@ -2101,7 +2101,7 @@
         <v>2030</v>
       </c>
       <c r="G70" s="17">
-        <v>0.63043461206223927</v>
+        <v>0.40978249784045556</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>73</v>
@@ -2118,7 +2118,7 @@
         <v>2030</v>
       </c>
       <c r="G71" s="17">
-        <v>0.42069713422261951</v>
+        <v>0.27345313724470272</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>73</v>
@@ -2135,7 +2135,7 @@
         <v>2030</v>
       </c>
       <c r="G72" s="16">
-        <v>0.20545403303996501</v>
+        <v>0.13354512147597727</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>73</v>
@@ -2152,7 +2152,7 @@
         <v>2030</v>
       </c>
       <c r="G73" s="16">
-        <v>3.1380889075732013E-2</v>
+        <v>2.0397577899225808E-2</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>73</v>
@@ -2373,7 +2373,7 @@
         <v>2030</v>
       </c>
       <c r="G86" s="16">
-        <v>0.12702061309745619</v>
+        <v>8.2563398513346528E-2</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>73</v>
@@ -2390,7 +2390,7 @@
         <v>2030</v>
       </c>
       <c r="G87" s="16">
-        <v>0.36346519701100283</v>
+        <v>0.23625237805715185</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>73</v>
@@ -2407,7 +2407,7 @@
         <v>2030</v>
       </c>
       <c r="G88" s="16">
-        <v>0.61379567340694685</v>
+        <v>0.39896718771451545</v>
       </c>
       <c r="I88" s="12" t="s">
         <v>73</v>
@@ -2424,7 +2424,7 @@
         <v>2030</v>
       </c>
       <c r="G89" s="16">
-        <v>0.81192460823347123</v>
+        <v>0.52775099535175629</v>
       </c>
       <c r="I89" s="12" t="s">
         <v>73</v>
@@ -2441,7 +2441,7 @@
         <v>2030</v>
       </c>
       <c r="G90" s="16">
-        <v>0.94826524408182478</v>
+        <v>0.6163724086531861</v>
       </c>
       <c r="I90" s="12" t="s">
         <v>73</v>
@@ -2458,7 +2458,7 @@
         <v>2030</v>
       </c>
       <c r="G91" s="16">
-        <v>1</v>
+        <v>0.65</v>
       </c>
       <c r="I91" s="12" t="s">
         <v>73</v>
@@ -2475,7 +2475,7 @@
         <v>2030</v>
       </c>
       <c r="G92" s="16">
-        <v>0.96893718006550689</v>
+        <v>0.6298091670425795</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>73</v>
@@ -2492,7 +2492,7 @@
         <v>2030</v>
       </c>
       <c r="G93" s="16">
-        <v>0.84461921666307094</v>
+        <v>0.54900249083099617</v>
       </c>
       <c r="I93" s="12" t="s">
         <v>73</v>
@@ -2509,7 +2509,7 @@
         <v>2030</v>
       </c>
       <c r="G94" s="16">
-        <v>0.65406476160589955</v>
+        <v>0.42514209504383471</v>
       </c>
       <c r="I94" s="12" t="s">
         <v>73</v>
@@ -2526,7 +2526,7 @@
         <v>2030</v>
       </c>
       <c r="G95" s="16">
-        <v>0.43068625335869931</v>
+        <v>0.27994606468315458</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>73</v>
@@ -2543,7 +2543,7 @@
         <v>2030</v>
       </c>
       <c r="G96" s="16">
-        <v>0.18066958244258341</v>
+        <v>0.11743522858767921</v>
       </c>
       <c r="I96" s="12" t="s">
         <v>73</v>
@@ -2560,7 +2560,7 @@
         <v>2030</v>
       </c>
       <c r="G97" s="16">
-        <v>1.3387726283170221E-2</v>
+        <v>8.7020220840606441E-3</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>73</v>

--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F49453C-6939-45D7-9100-50B952CAF692}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C85767-19DA-4B9A-B63C-A0FAA0E7743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,20 @@
     <sheet name="Trans Tables" sheetId="17" r:id="rId3"/>
     <sheet name="FILL Table" sheetId="19" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="125725"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1935,7 +1948,7 @@
         <v>2030</v>
       </c>
       <c r="G61" s="17">
-        <v>6.9165519713261618E-3</v>
+        <v>0</v>
       </c>
       <c r="I61" s="12" t="s">
         <v>73</v>
@@ -1952,7 +1965,7 @@
         <v>2030</v>
       </c>
       <c r="G62" s="17">
-        <v>4.9742853046594968E-2</v>
+        <v>5.604037815265784E-2</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>73</v>
@@ -1969,7 +1982,7 @@
         <v>2030</v>
       </c>
       <c r="G63" s="17">
-        <v>0.12554577777777776</v>
+        <v>0.18590092231523636</v>
       </c>
       <c r="I63" s="12" t="s">
         <v>73</v>
@@ -1986,7 +1999,7 @@
         <v>2030</v>
       </c>
       <c r="G64" s="17">
-        <v>0.2058007025089606</v>
+        <v>0.32440168678972731</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>73</v>
@@ -2003,7 +2016,7 @@
         <v>2030</v>
       </c>
       <c r="G65" s="17">
-        <v>0.27468446594982077</v>
+        <v>0.46004255347270961</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>73</v>
@@ -2020,7 +2033,7 @@
         <v>2030</v>
       </c>
       <c r="G66" s="17">
-        <v>0.32637437275985665</v>
+        <v>0.56566205921202428</v>
       </c>
       <c r="I66" s="12" t="s">
         <v>73</v>
@@ -2037,7 +2050,7 @@
         <v>2030</v>
       </c>
       <c r="G67" s="17">
-        <v>0.35267560573476697</v>
+        <v>0.60380916149981967</v>
       </c>
       <c r="I67" s="12" t="s">
         <v>73</v>
@@ -2054,7 +2067,7 @@
         <v>2030</v>
       </c>
       <c r="G68" s="17">
-        <v>0.34322033691756271</v>
+        <v>0.58623365205623601</v>
       </c>
       <c r="I68" s="12" t="s">
         <v>73</v>
@@ -2071,7 +2084,7 @@
         <v>2030</v>
       </c>
       <c r="G69" s="17">
-        <v>0.30308891039426522</v>
+        <v>0.52773436707225452</v>
       </c>
       <c r="I69" s="12" t="s">
         <v>73</v>
@@ -2088,7 +2101,7 @@
         <v>2030</v>
       </c>
       <c r="G70" s="17">
-        <v>0.23170381362007167</v>
+        <v>0.40978249784045556</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>73</v>
@@ -2105,7 +2118,7 @@
         <v>2030</v>
       </c>
       <c r="G71" s="17">
-        <v>0.14172651612903225</v>
+        <v>0.27345313724470272</v>
       </c>
       <c r="I71" s="12" t="s">
         <v>73</v>
@@ -2122,7 +2135,7 @@
         <v>2030</v>
       </c>
       <c r="G72" s="16">
-        <v>5.3895483870967743E-2</v>
+        <v>0.13354512147597727</v>
       </c>
       <c r="I72" s="12" t="s">
         <v>73</v>
@@ -2139,7 +2152,7 @@
         <v>2030</v>
       </c>
       <c r="G73" s="16">
-        <v>2.6301935483870969E-3</v>
+        <v>2.0397577899225808E-2</v>
       </c>
       <c r="I73" s="12" t="s">
         <v>73</v>
@@ -2343,7 +2356,7 @@
         <v>2030</v>
       </c>
       <c r="G85" s="16">
-        <v>6.4190919952210254E-3</v>
+        <v>0</v>
       </c>
       <c r="I85" s="12" t="s">
         <v>73</v>
@@ -2360,7 +2373,7 @@
         <v>2030</v>
       </c>
       <c r="G86" s="16">
-        <v>7.0838474313022717E-2</v>
+        <v>8.2563398513346528E-2</v>
       </c>
       <c r="I86" s="12" t="s">
         <v>73</v>
@@ -2377,7 +2390,7 @@
         <v>2030</v>
       </c>
       <c r="G87" s="16">
-        <v>0.15999428793309439</v>
+        <v>0.23625237805715185</v>
       </c>
       <c r="I87" s="12" t="s">
         <v>73</v>
@@ -2394,7 +2407,7 @@
         <v>2030</v>
       </c>
       <c r="G88" s="16">
-        <v>0.25343209199522099</v>
+        <v>0.39896718771451545</v>
       </c>
       <c r="I88" s="12" t="s">
         <v>73</v>
@@ -2411,7 +2424,7 @@
         <v>2030</v>
       </c>
       <c r="G89" s="16">
-        <v>0.32960197968936678</v>
+        <v>0.52775099535175629</v>
       </c>
       <c r="I89" s="12" t="s">
         <v>73</v>
@@ -2428,7 +2441,7 @@
         <v>2030</v>
       </c>
       <c r="G90" s="16">
-        <v>0.37592762246117079</v>
+        <v>0.6163724086531861</v>
       </c>
       <c r="I90" s="12" t="s">
         <v>73</v>
@@ -2445,7 +2458,7 @@
         <v>2030</v>
       </c>
       <c r="G91" s="16">
-        <v>0.38776096057347664</v>
+        <v>0.65</v>
       </c>
       <c r="I91" s="12" t="s">
         <v>73</v>
@@ -2462,7 +2475,7 @@
         <v>2030</v>
       </c>
       <c r="G92" s="16">
-        <v>0.36426783751493425</v>
+        <v>0.6298091670425795</v>
       </c>
       <c r="I92" s="12" t="s">
         <v>73</v>
@@ -2479,7 +2492,7 @@
         <v>2030</v>
       </c>
       <c r="G93" s="16">
-        <v>0.31009156033452806</v>
+        <v>0.54900249083099617</v>
       </c>
       <c r="I93" s="12" t="s">
         <v>73</v>
@@ -2496,7 +2509,7 @@
         <v>2030</v>
       </c>
       <c r="G94" s="16">
-        <v>0.23188419952210276</v>
+        <v>0.42514209504383471</v>
       </c>
       <c r="I94" s="12" t="s">
         <v>73</v>
@@ -2513,7 +2526,7 @@
         <v>2030</v>
       </c>
       <c r="G95" s="16">
-        <v>0.13618056033452808</v>
+        <v>0.27994606468315458</v>
       </c>
       <c r="I95" s="12" t="s">
         <v>73</v>
@@ -2530,7 +2543,7 @@
         <v>2030</v>
       </c>
       <c r="G96" s="16">
-        <v>4.9357593787335743E-2</v>
+        <v>0.11743522858767921</v>
       </c>
       <c r="I96" s="12" t="s">
         <v>73</v>
@@ -2547,7 +2560,7 @@
         <v>2030</v>
       </c>
       <c r="G97" s="16">
-        <v>7.5268817204301086E-6</v>
+        <v>8.7020220840606441E-3</v>
       </c>
       <c r="I97" s="12" t="s">
         <v>73</v>
@@ -2649,7 +2662,7 @@
         <v>2030</v>
       </c>
       <c r="G103" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I103" s="12" t="s">
         <v>74</v>
@@ -2666,7 +2679,7 @@
         <v>2030</v>
       </c>
       <c r="G104" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I104" s="12" t="s">
         <v>74</v>
@@ -2683,7 +2696,7 @@
         <v>2030</v>
       </c>
       <c r="G105" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I105" s="12" t="s">
         <v>74</v>
@@ -2700,7 +2713,7 @@
         <v>2030</v>
       </c>
       <c r="G106" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I106" s="12" t="s">
         <v>74</v>
@@ -2717,7 +2730,7 @@
         <v>2030</v>
       </c>
       <c r="G107" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I107" s="12" t="s">
         <v>74</v>
@@ -2734,7 +2747,7 @@
         <v>2030</v>
       </c>
       <c r="G108" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" s="12" t="s">
         <v>74</v>
@@ -2751,7 +2764,7 @@
         <v>2030</v>
       </c>
       <c r="G109" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I109" s="12" t="s">
         <v>74</v>
@@ -2768,7 +2781,7 @@
         <v>2030</v>
       </c>
       <c r="G110" s="16">
-        <v>1</v>
+        <v>0.1098256299077521</v>
       </c>
       <c r="I110" s="12" t="s">
         <v>74</v>
@@ -2785,7 +2798,7 @@
         <v>2030</v>
       </c>
       <c r="G111" s="16">
-        <v>1</v>
+        <v>0.26814642570934433</v>
       </c>
       <c r="I111" s="12" t="s">
         <v>74</v>
@@ -2802,7 +2815,7 @@
         <v>2030</v>
       </c>
       <c r="G112" s="16">
-        <v>1</v>
+        <v>0.41899992403164082</v>
       </c>
       <c r="I112" s="12" t="s">
         <v>74</v>
@@ -2819,7 +2832,7 @@
         <v>2030</v>
       </c>
       <c r="G113" s="16">
-        <v>1</v>
+        <v>0.57367160653674709</v>
       </c>
       <c r="I113" s="12" t="s">
         <v>74</v>
@@ -2836,7 +2849,7 @@
         <v>2030</v>
       </c>
       <c r="G114" s="16">
-        <v>1</v>
+        <v>0.68228556175917943</v>
       </c>
       <c r="I114" s="12" t="s">
         <v>74</v>
@@ -2853,7 +2866,7 @@
         <v>2030</v>
       </c>
       <c r="G115" s="16">
-        <v>1</v>
+        <v>0.7261312782791185</v>
       </c>
       <c r="I115" s="12" t="s">
         <v>74</v>
@@ -2870,7 +2883,7 @@
         <v>2030</v>
       </c>
       <c r="G116" s="16">
-        <v>1</v>
+        <v>0.72103097320835441</v>
       </c>
       <c r="I116" s="12" t="s">
         <v>74</v>
@@ -2887,7 +2900,7 @@
         <v>2030</v>
       </c>
       <c r="G117" s="16">
-        <v>1</v>
+        <v>0.71114032635841962</v>
       </c>
       <c r="I117" s="12" t="s">
         <v>74</v>
@@ -2904,7 +2917,7 @@
         <v>2030</v>
       </c>
       <c r="G118" s="16">
-        <v>1</v>
+        <v>0.56075177297351309</v>
       </c>
       <c r="I118" s="12" t="s">
         <v>74</v>
@@ -2921,7 +2934,7 @@
         <v>2030</v>
       </c>
       <c r="G119" s="16">
-        <v>1</v>
+        <v>0.41368828035297223</v>
       </c>
       <c r="I119" s="12" t="s">
         <v>74</v>
@@ -2938,7 +2951,7 @@
         <v>2030</v>
       </c>
       <c r="G120" s="16">
-        <v>1</v>
+        <v>0.25708637189567068</v>
       </c>
       <c r="I120" s="12" t="s">
         <v>74</v>
@@ -2955,7 +2968,7 @@
         <v>2030</v>
       </c>
       <c r="G121" s="16">
-        <v>1</v>
+        <v>3.608254498957706E-2</v>
       </c>
       <c r="I121" s="12" t="s">
         <v>74</v>
@@ -2972,7 +2985,7 @@
         <v>2030</v>
       </c>
       <c r="G122" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" s="12" t="s">
         <v>74</v>
@@ -2989,7 +3002,7 @@
         <v>2030</v>
       </c>
       <c r="G123" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I123" s="12" t="s">
         <v>74</v>
@@ -3006,7 +3019,7 @@
         <v>2030</v>
       </c>
       <c r="G124" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I124" s="12" t="s">
         <v>74</v>
@@ -3023,7 +3036,7 @@
         <v>2030</v>
       </c>
       <c r="G125" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I125" s="12" t="s">
         <v>74</v>
@@ -3040,7 +3053,7 @@
         <v>2030</v>
       </c>
       <c r="G126" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I126" s="12" t="s">
         <v>74</v>
@@ -3057,7 +3070,7 @@
         <v>2030</v>
       </c>
       <c r="G127" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I127" s="12" t="s">
         <v>74</v>
@@ -3074,7 +3087,7 @@
         <v>2030</v>
       </c>
       <c r="G128" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I128" s="12" t="s">
         <v>74</v>
@@ -3091,7 +3104,7 @@
         <v>2030</v>
       </c>
       <c r="G129" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I129" s="12" t="s">
         <v>74</v>
@@ -3108,7 +3121,7 @@
         <v>2030</v>
       </c>
       <c r="G130" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I130" s="12" t="s">
         <v>74</v>
@@ -3125,7 +3138,7 @@
         <v>2030</v>
       </c>
       <c r="G131" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I131" s="12" t="s">
         <v>74</v>
@@ -3142,7 +3155,7 @@
         <v>2030</v>
       </c>
       <c r="G132" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I132" s="12" t="s">
         <v>74</v>
@@ -3159,7 +3172,7 @@
         <v>2030</v>
       </c>
       <c r="G133" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I133" s="12" t="s">
         <v>74</v>
@@ -3176,7 +3189,7 @@
         <v>2030</v>
       </c>
       <c r="G134" s="16">
-        <v>1</v>
+        <v>0.3345361656869914</v>
       </c>
       <c r="I134" s="12" t="s">
         <v>74</v>
@@ -3193,7 +3206,7 @@
         <v>2030</v>
       </c>
       <c r="G135" s="16">
-        <v>1</v>
+        <v>0.60225815947657801</v>
       </c>
       <c r="I135" s="12" t="s">
         <v>74</v>
@@ -3210,7 +3223,7 @@
         <v>2030</v>
       </c>
       <c r="G136" s="16">
-        <v>1</v>
+        <v>0.80494648978700378</v>
       </c>
       <c r="I136" s="12" t="s">
         <v>74</v>
@@ -3227,7 +3240,7 @@
         <v>2030</v>
       </c>
       <c r="G137" s="16">
-        <v>1</v>
+        <v>0.91440739931818404</v>
       </c>
       <c r="I137" s="12" t="s">
         <v>74</v>
@@ -3244,7 +3257,7 @@
         <v>2030</v>
       </c>
       <c r="G138" s="16">
-        <v>1</v>
+        <v>0.97058600093061254</v>
       </c>
       <c r="I138" s="12" t="s">
         <v>74</v>
@@ -3261,7 +3274,7 @@
         <v>2030</v>
       </c>
       <c r="G139" s="16">
-        <v>1</v>
+        <v>0.998888962747016</v>
       </c>
       <c r="I139" s="12" t="s">
         <v>74</v>
@@ -3295,7 +3308,7 @@
         <v>2030</v>
       </c>
       <c r="G141" s="16">
-        <v>1</v>
+        <v>0.94102481316531672</v>
       </c>
       <c r="I141" s="12" t="s">
         <v>74</v>
@@ -3312,7 +3325,7 @@
         <v>2030</v>
       </c>
       <c r="G142" s="16">
-        <v>1</v>
+        <v>0.84154899484364765</v>
       </c>
       <c r="I142" s="12" t="s">
         <v>74</v>
@@ -3329,7 +3342,7 @@
         <v>2030</v>
       </c>
       <c r="G143" s="16">
-        <v>1</v>
+        <v>0.72343718841102689</v>
       </c>
       <c r="I143" s="12" t="s">
         <v>74</v>
@@ -3346,7 +3359,7 @@
         <v>2030</v>
       </c>
       <c r="G144" s="16">
-        <v>1</v>
+        <v>0.46359691188619939</v>
       </c>
       <c r="I144" s="12" t="s">
         <v>74</v>
@@ -3363,7 +3376,7 @@
         <v>2030</v>
       </c>
       <c r="G145" s="16">
-        <v>1</v>
+        <v>3.8326037205503913E-2</v>
       </c>
       <c r="I145" s="12" t="s">
         <v>74</v>
@@ -3380,7 +3393,7 @@
         <v>2030</v>
       </c>
       <c r="G146" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146" s="12" t="s">
         <v>74</v>
@@ -3397,7 +3410,7 @@
         <v>2030</v>
       </c>
       <c r="G147" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I147" s="12" t="s">
         <v>74</v>
@@ -3414,7 +3427,7 @@
         <v>2030</v>
       </c>
       <c r="G148" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I148" s="12" t="s">
         <v>74</v>
@@ -3431,7 +3444,7 @@
         <v>2030</v>
       </c>
       <c r="G149" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I149" s="12" t="s">
         <v>74</v>
@@ -3448,7 +3461,7 @@
         <v>2030</v>
       </c>
       <c r="G150" s="16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I150" s="12" t="s">
         <v>74</v>

--- a/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_NewTechs_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\IND001\MANU2025\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C85767-19DA-4B9A-B63C-A0FAA0E7743E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64962DF7-391B-4D4E-9788-6B8017CE8F98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AF_Trans" sheetId="20" r:id="rId1"/>
@@ -18,6 +18,9 @@
     <sheet name="Trans Tables" sheetId="17" r:id="rId3"/>
     <sheet name="FILL Table" sheetId="19" r:id="rId4"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId5"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -645,6 +648,598 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="A1" t="str">
+            <v>Time</v>
+          </cell>
+          <cell r="B1" t="str">
+            <v xml:space="preserve">WINDELC-Annual </v>
+          </cell>
+          <cell r="C1" t="str">
+            <v>WINDELC-WETSEASON</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>WINDELC-DRYSEASON</v>
+          </cell>
+          <cell r="E1" t="str">
+            <v xml:space="preserve">SOLAR PV-Annual </v>
+          </cell>
+          <cell r="F1" t="str">
+            <v>SOLAR PV-WETSEASON</v>
+          </cell>
+          <cell r="G1" t="str">
+            <v>SOLAR PV-DRYSEASON</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2">
+            <v>1</v>
+          </cell>
+          <cell r="B2">
+            <v>3.3051976250754521E-3</v>
+          </cell>
+          <cell r="C2">
+            <v>3.3051976250754521E-3</v>
+          </cell>
+          <cell r="D2">
+            <v>3.3051976250754521E-3</v>
+          </cell>
+          <cell r="E2">
+            <v>0</v>
+          </cell>
+          <cell r="F2">
+            <v>0</v>
+          </cell>
+          <cell r="G2">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3">
+            <v>2</v>
+          </cell>
+          <cell r="B3">
+            <v>3.1618331753269246E-3</v>
+          </cell>
+          <cell r="C3">
+            <v>3.1618331753269246E-3</v>
+          </cell>
+          <cell r="D3">
+            <v>3.1618331753269246E-3</v>
+          </cell>
+          <cell r="E3">
+            <v>0</v>
+          </cell>
+          <cell r="F3">
+            <v>0</v>
+          </cell>
+          <cell r="G3">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4">
+            <v>3</v>
+          </cell>
+          <cell r="B4">
+            <v>2.8979409360310663E-3</v>
+          </cell>
+          <cell r="C4">
+            <v>2.8979409360310663E-3</v>
+          </cell>
+          <cell r="D4">
+            <v>2.8979409360310663E-3</v>
+          </cell>
+          <cell r="E4">
+            <v>0</v>
+          </cell>
+          <cell r="F4">
+            <v>0</v>
+          </cell>
+          <cell r="G4">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5">
+            <v>4</v>
+          </cell>
+          <cell r="B5">
+            <v>2.7156926103261707E-3</v>
+          </cell>
+          <cell r="C5">
+            <v>2.7156926103261707E-3</v>
+          </cell>
+          <cell r="D5">
+            <v>2.7156926103261707E-3</v>
+          </cell>
+          <cell r="E5">
+            <v>0</v>
+          </cell>
+          <cell r="F5">
+            <v>0</v>
+          </cell>
+          <cell r="G5">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6">
+            <v>5</v>
+          </cell>
+          <cell r="B6">
+            <v>2.5452192095824343E-3</v>
+          </cell>
+          <cell r="C6">
+            <v>2.5452192095824343E-3</v>
+          </cell>
+          <cell r="D6">
+            <v>2.5452192095824343E-3</v>
+          </cell>
+          <cell r="E6">
+            <v>0</v>
+          </cell>
+          <cell r="F6">
+            <v>0</v>
+          </cell>
+          <cell r="G6">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7">
+            <v>6</v>
+          </cell>
+          <cell r="B7">
+            <v>2.5834450529081338E-3</v>
+          </cell>
+          <cell r="C7">
+            <v>2.5834450529081338E-3</v>
+          </cell>
+          <cell r="D7">
+            <v>2.5834450529081338E-3</v>
+          </cell>
+          <cell r="E7">
+            <v>0</v>
+          </cell>
+          <cell r="F7">
+            <v>0</v>
+          </cell>
+          <cell r="G7">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8">
+            <v>7</v>
+          </cell>
+          <cell r="B8">
+            <v>2.7432881310744312E-3</v>
+          </cell>
+          <cell r="C8">
+            <v>2.7432881310744317E-3</v>
+          </cell>
+          <cell r="D8">
+            <v>2.7432881310744317E-3</v>
+          </cell>
+          <cell r="E8">
+            <v>0</v>
+          </cell>
+          <cell r="F8">
+            <v>0</v>
+          </cell>
+          <cell r="G8">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="A9">
+            <v>8</v>
+          </cell>
+          <cell r="B9">
+            <v>2.8314721319216154E-3</v>
+          </cell>
+          <cell r="C9">
+            <v>2.8314721319216154E-3</v>
+          </cell>
+          <cell r="D9">
+            <v>2.8314721319216154E-3</v>
+          </cell>
+          <cell r="E9">
+            <v>7.5932643423174351E-2</v>
+          </cell>
+          <cell r="F9">
+            <v>5.604037815265784E-2</v>
+          </cell>
+          <cell r="G9">
+            <v>8.2563398513346528E-2</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="A10">
+            <v>9</v>
+          </cell>
+          <cell r="B10">
+            <v>2.8141143326017269E-3</v>
+          </cell>
+          <cell r="C10">
+            <v>2.8141143326017269E-3</v>
+          </cell>
+          <cell r="D10">
+            <v>2.8141143326017269E-3</v>
+          </cell>
+          <cell r="E10">
+            <v>0.22366451412167299</v>
+          </cell>
+          <cell r="F10">
+            <v>0.18590092231523636</v>
+          </cell>
+          <cell r="G10">
+            <v>0.23625237805715185</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="A11">
+            <v>10</v>
+          </cell>
+          <cell r="B11">
+            <v>2.6656478128544076E-3</v>
+          </cell>
+          <cell r="C11">
+            <v>2.6656478128544076E-3</v>
+          </cell>
+          <cell r="D11">
+            <v>2.6656478128544076E-3</v>
+          </cell>
+          <cell r="E11">
+            <v>0.38032581248331843</v>
+          </cell>
+          <cell r="F11">
+            <v>0.32440168678972731</v>
+          </cell>
+          <cell r="G11">
+            <v>0.39896718771451545</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="A12">
+            <v>11</v>
+          </cell>
+          <cell r="B12">
+            <v>2.4530677112863486E-3</v>
+          </cell>
+          <cell r="C12">
+            <v>2.4530677112863486E-3</v>
+          </cell>
+          <cell r="D12">
+            <v>2.4530677112863486E-3</v>
+          </cell>
+          <cell r="E12">
+            <v>0.51082388488199459</v>
+          </cell>
+          <cell r="F12">
+            <v>0.46004255347270961</v>
+          </cell>
+          <cell r="G12">
+            <v>0.52775099535175629</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="A13">
+            <v>12</v>
+          </cell>
+          <cell r="B13">
+            <v>2.1363241345921055E-3</v>
+          </cell>
+          <cell r="C13">
+            <v>2.1363241345921055E-3</v>
+          </cell>
+          <cell r="D13">
+            <v>2.1363241345921055E-3</v>
+          </cell>
+          <cell r="E13">
+            <v>0.60369482129289564</v>
+          </cell>
+          <cell r="F13">
+            <v>0.56566205921202428</v>
+          </cell>
+          <cell r="G13">
+            <v>0.6163724086531861</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="A14">
+            <v>13</v>
+          </cell>
+          <cell r="B14">
+            <v>1.8660639529435976E-3</v>
+          </cell>
+          <cell r="C14">
+            <v>1.8660639529435976E-3</v>
+          </cell>
+          <cell r="D14">
+            <v>1.8660639529435976E-3</v>
+          </cell>
+          <cell r="E14">
+            <v>0.63845229037495488</v>
+          </cell>
+          <cell r="F14">
+            <v>0.60380916149981967</v>
+          </cell>
+          <cell r="G14">
+            <v>0.65</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="A15">
+            <v>14</v>
+          </cell>
+          <cell r="B15">
+            <v>1.7487528282965712E-3</v>
+          </cell>
+          <cell r="C15">
+            <v>1.7487528282965712E-3</v>
+          </cell>
+          <cell r="D15">
+            <v>1.7487528282965712E-3</v>
+          </cell>
+          <cell r="E15">
+            <v>0.61891528829599363</v>
+          </cell>
+          <cell r="F15">
+            <v>0.58623365205623601</v>
+          </cell>
+          <cell r="G15">
+            <v>0.6298091670425795</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="A16">
+            <v>15</v>
+          </cell>
+          <cell r="B16">
+            <v>1.6637860863902745E-3</v>
+          </cell>
+          <cell r="C16">
+            <v>1.6637860863902745E-3</v>
+          </cell>
+          <cell r="D16">
+            <v>1.6637860863902745E-3</v>
+          </cell>
+          <cell r="E16">
+            <v>0.54368545989131078</v>
+          </cell>
+          <cell r="F16">
+            <v>0.52773436707225452</v>
+          </cell>
+          <cell r="G16">
+            <v>0.54900249083099617</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="A17">
+            <v>16</v>
+          </cell>
+          <cell r="B17">
+            <v>1.8211742012316831E-3</v>
+          </cell>
+          <cell r="C17">
+            <v>1.8211742012316831E-3</v>
+          </cell>
+          <cell r="D17">
+            <v>1.8211742012316831E-3</v>
+          </cell>
+          <cell r="E17">
+            <v>0.42130219574298994</v>
+          </cell>
+          <cell r="F17">
+            <v>0.40978249784045556</v>
+          </cell>
+          <cell r="G17">
+            <v>0.42514209504383471</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="A18">
+            <v>17</v>
+          </cell>
+          <cell r="B18">
+            <v>1.9153018835258307E-3</v>
+          </cell>
+          <cell r="C18">
+            <v>1.9153018835258307E-3</v>
+          </cell>
+          <cell r="D18">
+            <v>1.9153018835258307E-3</v>
+          </cell>
+          <cell r="E18">
+            <v>0.27832283282354164</v>
+          </cell>
+          <cell r="F18">
+            <v>0.27345313724470272</v>
+          </cell>
+          <cell r="G18">
+            <v>0.27994606468315458</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="A19">
+            <v>18</v>
+          </cell>
+          <cell r="B19">
+            <v>1.9744590518638132E-3</v>
+          </cell>
+          <cell r="C19">
+            <v>1.9744590518638132E-3</v>
+          </cell>
+          <cell r="D19">
+            <v>1.9744590518638132E-3</v>
+          </cell>
+          <cell r="E19">
+            <v>0.12146270180975371</v>
+          </cell>
+          <cell r="F19">
+            <v>0.13354512147597727</v>
+          </cell>
+          <cell r="G19">
+            <v>0.11743522858767921</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="A20">
+            <v>19</v>
+          </cell>
+          <cell r="B20">
+            <v>2.1878436160058393E-3</v>
+          </cell>
+          <cell r="C20">
+            <v>2.1878436160058393E-3</v>
+          </cell>
+          <cell r="D20">
+            <v>2.1878436160058393E-3</v>
+          </cell>
+          <cell r="E20">
+            <v>1.1625911037851938E-2</v>
+          </cell>
+          <cell r="F20">
+            <v>2.0397577899225808E-2</v>
+          </cell>
+          <cell r="G20">
+            <v>8.7020220840606441E-3</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="A21">
+            <v>20</v>
+          </cell>
+          <cell r="B21">
+            <v>2.3889741533883327E-3</v>
+          </cell>
+          <cell r="C21">
+            <v>2.3889741533883327E-3</v>
+          </cell>
+          <cell r="D21">
+            <v>2.3889741533883327E-3</v>
+          </cell>
+          <cell r="E21">
+            <v>0</v>
+          </cell>
+          <cell r="F21">
+            <v>0</v>
+          </cell>
+          <cell r="G21">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="A22">
+            <v>21</v>
+          </cell>
+          <cell r="B22">
+            <v>2.4063426997311056E-3</v>
+          </cell>
+          <cell r="C22">
+            <v>2.4063426997311056E-3</v>
+          </cell>
+          <cell r="D22">
+            <v>2.4063426997311056E-3</v>
+          </cell>
+          <cell r="E22">
+            <v>0</v>
+          </cell>
+          <cell r="F22">
+            <v>0</v>
+          </cell>
+          <cell r="G22">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="A23">
+            <v>22</v>
+          </cell>
+          <cell r="B23">
+            <v>2.5925256698099051E-3</v>
+          </cell>
+          <cell r="C23">
+            <v>2.5925256698099051E-3</v>
+          </cell>
+          <cell r="D23">
+            <v>2.5925256698099051E-3</v>
+          </cell>
+          <cell r="E23">
+            <v>0</v>
+          </cell>
+          <cell r="F23">
+            <v>0</v>
+          </cell>
+          <cell r="G23">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="A24">
+            <v>23</v>
+          </cell>
+          <cell r="B24">
+            <v>2.9724559200622644E-3</v>
+          </cell>
+          <cell r="C24">
+            <v>2.9724559200622644E-3</v>
+          </cell>
+          <cell r="D24">
+            <v>2.9724559200622644E-3</v>
+          </cell>
+          <cell r="E24">
+            <v>0</v>
+          </cell>
+          <cell r="F24">
+            <v>0</v>
+          </cell>
+          <cell r="G24">
+            <v>0</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="A25">
+            <v>24</v>
+          </cell>
+          <cell r="B25">
+            <v>3.3823091606694383E-3</v>
+          </cell>
+          <cell r="C25">
+            <v>3.3823091606694387E-3</v>
+          </cell>
+          <cell r="D25">
+            <v>3.3823091606694387E-3</v>
+          </cell>
+          <cell r="E25">
+            <v>0</v>
+          </cell>
+          <cell r="F25">
+            <v>0</v>
+          </cell>
+          <cell r="G25">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1080,7 +1675,7 @@
       <c r="E10">
         <v>2030</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="13">
         <v>2.7156926103261707E-3</v>
       </c>
       <c r="I10" s="12" t="s">
